--- a/listings.tsv.xlsx
+++ b/listings.tsv.xlsx
@@ -8,19 +8,22 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/831e68cdec78212b/Documents/GitHub/haniproperties/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{C8439A61-B804-44A5-B5F8-615007BB98B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="6" documentId="8_{C8439A61-B804-44A5-B5F8-615007BB98B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{064FCB6B-C229-49C8-92D4-85E0AFAC8D3A}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{65CABF58-D2E8-4A2E-8EC9-ED571570DEC3}"/>
   </bookViews>
   <sheets>
     <sheet name="listings_2" sheetId="1" r:id="rId1"/>
   </sheets>
+  <definedNames>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">listings_2!$A$1:$R$833</definedName>
+  </definedNames>
   <calcPr calcId="0"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7493" uniqueCount="3493">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7494" uniqueCount="3494">
   <si>
     <t>listing_type</t>
   </si>
@@ -10499,13 +10502,16 @@
   </si>
   <si>
     <t>https://t.me/extremeproperty_listing/19071</t>
+  </si>
+  <si>
+    <t>image/Vista Alam|Vista Alam1|Vista Alam2</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="18" x14ac:knownFonts="1">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -10636,6 +10642,14 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color theme="10"/>
       <name val="Aptos Narrow"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -10944,7 +10958,7 @@
       <diagonal/>
     </border>
   </borders>
-  <cellStyleXfs count="42">
+  <cellStyleXfs count="43">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0"/>
@@ -10987,13 +11001,15 @@
     <xf numFmtId="0" fontId="1" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="3">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="14" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="0" fillId="33" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="42"/>
   </cellXfs>
-  <cellStyles count="42">
+  <cellStyles count="43">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
     <cellStyle name="20% - Accent2" xfId="23" builtinId="34" customBuiltin="1"/>
     <cellStyle name="20% - Accent3" xfId="27" builtinId="38" customBuiltin="1"/>
@@ -11027,6 +11043,7 @@
     <cellStyle name="Heading 2" xfId="3" builtinId="17" customBuiltin="1"/>
     <cellStyle name="Heading 3" xfId="4" builtinId="18" customBuiltin="1"/>
     <cellStyle name="Heading 4" xfId="5" builtinId="19" customBuiltin="1"/>
+    <cellStyle name="Hyperlink" xfId="42" builtinId="8"/>
     <cellStyle name="Input" xfId="9" builtinId="20" customBuiltin="1"/>
     <cellStyle name="Linked Cell" xfId="12" builtinId="24" customBuiltin="1"/>
     <cellStyle name="Neutral" xfId="8" builtinId="28" customBuiltin="1"/>
@@ -11367,6 +11384,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{32D9BDB5-49E3-4F0A-992F-D41F604492EC}">
+  <sheetPr filterMode="1"/>
   <dimension ref="A1:R833"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
@@ -11384,7 +11402,7 @@
     <col min="12" max="12" width="14.33203125" bestFit="1" customWidth="1"/>
     <col min="13" max="13" width="16.5546875" bestFit="1" customWidth="1"/>
     <col min="14" max="14" width="191.44140625" bestFit="1" customWidth="1"/>
-    <col min="15" max="15" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="15" max="15" width="46" customWidth="1"/>
     <col min="16" max="16" width="124.44140625" bestFit="1" customWidth="1"/>
     <col min="17" max="17" width="10.33203125" bestFit="1" customWidth="1"/>
     <col min="18" max="18" width="161.6640625" bestFit="1" customWidth="1"/>
@@ -11446,7 +11464,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="2" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>18</v>
       </c>
@@ -11490,7 +11508,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="3" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>18</v>
       </c>
@@ -11534,7 +11552,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="4" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>18</v>
       </c>
@@ -11578,7 +11596,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="5" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A5" t="s">
         <v>18</v>
       </c>
@@ -11622,7 +11640,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="6" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>18</v>
       </c>
@@ -11666,7 +11684,7 @@
         <v>44</v>
       </c>
     </row>
-    <row r="7" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>18</v>
       </c>
@@ -11710,7 +11728,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="8" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A8" t="s">
         <v>18</v>
       </c>
@@ -11754,7 +11772,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="9" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A9" t="s">
         <v>18</v>
       </c>
@@ -11798,7 +11816,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="10" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A10" t="s">
         <v>18</v>
       </c>
@@ -11842,7 +11860,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="11" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A11" t="s">
         <v>18</v>
       </c>
@@ -11886,7 +11904,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="12" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A12" t="s">
         <v>18</v>
       </c>
@@ -11930,7 +11948,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="13" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A13" t="s">
         <v>18</v>
       </c>
@@ -11974,7 +11992,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="14" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A14" t="s">
         <v>18</v>
       </c>
@@ -12052,17 +12070,20 @@
       <c r="N15" t="s">
         <v>87</v>
       </c>
+      <c r="O15" t="s">
+        <v>3493</v>
+      </c>
       <c r="P15" t="s">
         <v>88</v>
       </c>
       <c r="Q15" s="1">
         <v>46189</v>
       </c>
-      <c r="R15" t="s">
+      <c r="R15" s="3" t="s">
         <v>89</v>
       </c>
     </row>
-    <row r="16" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A16" t="s">
         <v>18</v>
       </c>
@@ -12106,7 +12127,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="17" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A17" t="s">
         <v>18</v>
       </c>
@@ -12150,7 +12171,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="18" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A18" t="s">
         <v>18</v>
       </c>
@@ -12238,7 +12259,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="20" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A20" t="s">
         <v>18</v>
       </c>
@@ -12282,7 +12303,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="21" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A21" t="s">
         <v>18</v>
       </c>
@@ -12326,7 +12347,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="22" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A22" t="s">
         <v>18</v>
       </c>
@@ -12414,7 +12435,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="24" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A24" t="s">
         <v>18</v>
       </c>
@@ -12458,7 +12479,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="25" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A25" t="s">
         <v>18</v>
       </c>
@@ -12502,7 +12523,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="26" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A26" t="s">
         <v>18</v>
       </c>
@@ -12546,7 +12567,7 @@
         <v>145</v>
       </c>
     </row>
-    <row r="27" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A27" t="s">
         <v>18</v>
       </c>
@@ -12590,7 +12611,7 @@
         <v>151</v>
       </c>
     </row>
-    <row r="28" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A28" t="s">
         <v>18</v>
       </c>
@@ -12634,7 +12655,7 @@
         <v>153</v>
       </c>
     </row>
-    <row r="29" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A29" t="s">
         <v>18</v>
       </c>
@@ -12678,7 +12699,7 @@
         <v>158</v>
       </c>
     </row>
-    <row r="30" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A30" t="s">
         <v>18</v>
       </c>
@@ -12722,7 +12743,7 @@
         <v>162</v>
       </c>
     </row>
-    <row r="31" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A31" t="s">
         <v>18</v>
       </c>
@@ -12766,7 +12787,7 @@
         <v>167</v>
       </c>
     </row>
-    <row r="32" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A32" t="s">
         <v>18</v>
       </c>
@@ -12807,7 +12828,7 @@
         <v>172</v>
       </c>
     </row>
-    <row r="33" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A33" t="s">
         <v>18</v>
       </c>
@@ -12851,7 +12872,7 @@
         <v>177</v>
       </c>
     </row>
-    <row r="34" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A34" t="s">
         <v>18</v>
       </c>
@@ -12895,7 +12916,7 @@
         <v>179</v>
       </c>
     </row>
-    <row r="35" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A35" t="s">
         <v>18</v>
       </c>
@@ -12939,7 +12960,7 @@
         <v>184</v>
       </c>
     </row>
-    <row r="36" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A36" t="s">
         <v>18</v>
       </c>
@@ -12983,7 +13004,7 @@
         <v>189</v>
       </c>
     </row>
-    <row r="37" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A37" t="s">
         <v>18</v>
       </c>
@@ -13027,7 +13048,7 @@
         <v>194</v>
       </c>
     </row>
-    <row r="38" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A38" t="s">
         <v>18</v>
       </c>
@@ -13071,7 +13092,7 @@
         <v>199</v>
       </c>
     </row>
-    <row r="39" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A39" t="s">
         <v>18</v>
       </c>
@@ -13115,7 +13136,7 @@
         <v>204</v>
       </c>
     </row>
-    <row r="40" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A40" t="s">
         <v>18</v>
       </c>
@@ -13159,7 +13180,7 @@
         <v>208</v>
       </c>
     </row>
-    <row r="41" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A41" t="s">
         <v>18</v>
       </c>
@@ -13203,7 +13224,7 @@
         <v>212</v>
       </c>
     </row>
-    <row r="42" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A42" t="s">
         <v>18</v>
       </c>
@@ -13247,7 +13268,7 @@
         <v>217</v>
       </c>
     </row>
-    <row r="43" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A43" t="s">
         <v>18</v>
       </c>
@@ -13291,7 +13312,7 @@
         <v>221</v>
       </c>
     </row>
-    <row r="44" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A44" t="s">
         <v>18</v>
       </c>
@@ -13335,7 +13356,7 @@
         <v>226</v>
       </c>
     </row>
-    <row r="45" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A45" t="s">
         <v>18</v>
       </c>
@@ -13379,7 +13400,7 @@
         <v>231</v>
       </c>
     </row>
-    <row r="46" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A46" t="s">
         <v>18</v>
       </c>
@@ -13423,7 +13444,7 @@
         <v>233</v>
       </c>
     </row>
-    <row r="47" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A47" t="s">
         <v>18</v>
       </c>
@@ -13467,7 +13488,7 @@
         <v>237</v>
       </c>
     </row>
-    <row r="48" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A48" t="s">
         <v>18</v>
       </c>
@@ -13511,7 +13532,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="49" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A49" t="s">
         <v>18</v>
       </c>
@@ -13555,7 +13576,7 @@
         <v>248</v>
       </c>
     </row>
-    <row r="50" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="50" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A50" t="s">
         <v>18</v>
       </c>
@@ -13599,7 +13620,7 @@
         <v>254</v>
       </c>
     </row>
-    <row r="51" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="51" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A51" t="s">
         <v>18</v>
       </c>
@@ -13643,7 +13664,7 @@
         <v>259</v>
       </c>
     </row>
-    <row r="52" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="52" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A52" t="s">
         <v>18</v>
       </c>
@@ -13687,7 +13708,7 @@
         <v>264</v>
       </c>
     </row>
-    <row r="53" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="53" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A53" t="s">
         <v>18</v>
       </c>
@@ -13731,7 +13752,7 @@
         <v>270</v>
       </c>
     </row>
-    <row r="54" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="54" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A54" t="s">
         <v>18</v>
       </c>
@@ -13775,7 +13796,7 @@
         <v>275</v>
       </c>
     </row>
-    <row r="55" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="55" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A55" t="s">
         <v>18</v>
       </c>
@@ -13819,7 +13840,7 @@
         <v>281</v>
       </c>
     </row>
-    <row r="56" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="56" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A56" t="s">
         <v>18</v>
       </c>
@@ -13863,7 +13884,7 @@
         <v>284</v>
       </c>
     </row>
-    <row r="57" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="57" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A57" t="s">
         <v>18</v>
       </c>
@@ -13907,7 +13928,7 @@
         <v>289</v>
       </c>
     </row>
-    <row r="58" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="58" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A58" t="s">
         <v>18</v>
       </c>
@@ -13951,7 +13972,7 @@
         <v>295</v>
       </c>
     </row>
-    <row r="59" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="59" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A59" t="s">
         <v>18</v>
       </c>
@@ -13995,7 +14016,7 @@
         <v>300</v>
       </c>
     </row>
-    <row r="60" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="60" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A60" t="s">
         <v>18</v>
       </c>
@@ -14039,7 +14060,7 @@
         <v>305</v>
       </c>
     </row>
-    <row r="61" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="61" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A61" t="s">
         <v>18</v>
       </c>
@@ -14083,7 +14104,7 @@
         <v>310</v>
       </c>
     </row>
-    <row r="62" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="62" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A62" t="s">
         <v>18</v>
       </c>
@@ -14168,7 +14189,7 @@
         <v>319</v>
       </c>
     </row>
-    <row r="64" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="64" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A64" t="s">
         <v>18</v>
       </c>
@@ -14256,7 +14277,7 @@
         <v>330</v>
       </c>
     </row>
-    <row r="66" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="66" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A66" t="s">
         <v>18</v>
       </c>
@@ -14300,7 +14321,7 @@
         <v>335</v>
       </c>
     </row>
-    <row r="67" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="67" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A67" t="s">
         <v>18</v>
       </c>
@@ -14344,7 +14365,7 @@
         <v>339</v>
       </c>
     </row>
-    <row r="68" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="68" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A68" t="s">
         <v>18</v>
       </c>
@@ -14388,7 +14409,7 @@
         <v>343</v>
       </c>
     </row>
-    <row r="69" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="69" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A69" t="s">
         <v>18</v>
       </c>
@@ -14432,7 +14453,7 @@
         <v>348</v>
       </c>
     </row>
-    <row r="70" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="70" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A70" t="s">
         <v>18</v>
       </c>
@@ -14476,7 +14497,7 @@
         <v>352</v>
       </c>
     </row>
-    <row r="71" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="71" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A71" t="s">
         <v>18</v>
       </c>
@@ -14520,7 +14541,7 @@
         <v>356</v>
       </c>
     </row>
-    <row r="72" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="72" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A72" t="s">
         <v>18</v>
       </c>
@@ -14564,7 +14585,7 @@
         <v>359</v>
       </c>
     </row>
-    <row r="73" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="73" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A73" t="s">
         <v>18</v>
       </c>
@@ -14608,7 +14629,7 @@
         <v>364</v>
       </c>
     </row>
-    <row r="74" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="74" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A74" t="s">
         <v>18</v>
       </c>
@@ -14652,7 +14673,7 @@
         <v>369</v>
       </c>
     </row>
-    <row r="75" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="75" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A75" t="s">
         <v>18</v>
       </c>
@@ -14740,7 +14761,7 @@
         <v>377</v>
       </c>
     </row>
-    <row r="77" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="77" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A77" t="s">
         <v>18</v>
       </c>
@@ -14784,7 +14805,7 @@
         <v>382</v>
       </c>
     </row>
-    <row r="78" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="78" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A78" t="s">
         <v>18</v>
       </c>
@@ -14828,7 +14849,7 @@
         <v>386</v>
       </c>
     </row>
-    <row r="79" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="79" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A79" t="s">
         <v>18</v>
       </c>
@@ -14872,7 +14893,7 @@
         <v>392</v>
       </c>
     </row>
-    <row r="80" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="80" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A80" t="s">
         <v>18</v>
       </c>
@@ -14916,7 +14937,7 @@
         <v>396</v>
       </c>
     </row>
-    <row r="81" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="81" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A81" t="s">
         <v>18</v>
       </c>
@@ -15048,7 +15069,7 @@
         <v>410</v>
       </c>
     </row>
-    <row r="84" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="84" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A84" t="s">
         <v>18</v>
       </c>
@@ -15092,7 +15113,7 @@
         <v>414</v>
       </c>
     </row>
-    <row r="85" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="85" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A85" t="s">
         <v>18</v>
       </c>
@@ -15136,7 +15157,7 @@
         <v>419</v>
       </c>
     </row>
-    <row r="86" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="86" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A86" t="s">
         <v>18</v>
       </c>
@@ -15180,7 +15201,7 @@
         <v>423</v>
       </c>
     </row>
-    <row r="87" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="87" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A87" t="s">
         <v>18</v>
       </c>
@@ -15356,7 +15377,7 @@
         <v>442</v>
       </c>
     </row>
-    <row r="91" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="91" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A91" t="s">
         <v>18</v>
       </c>
@@ -15400,7 +15421,7 @@
         <v>447</v>
       </c>
     </row>
-    <row r="92" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="92" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A92" t="s">
         <v>18</v>
       </c>
@@ -15444,7 +15465,7 @@
         <v>452</v>
       </c>
     </row>
-    <row r="93" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="93" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A93" t="s">
         <v>18</v>
       </c>
@@ -15488,7 +15509,7 @@
         <v>456</v>
       </c>
     </row>
-    <row r="94" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="94" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A94" t="s">
         <v>18</v>
       </c>
@@ -15532,7 +15553,7 @@
         <v>458</v>
       </c>
     </row>
-    <row r="95" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="95" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A95" t="s">
         <v>18</v>
       </c>
@@ -15576,7 +15597,7 @@
         <v>463</v>
       </c>
     </row>
-    <row r="96" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="96" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A96" t="s">
         <v>18</v>
       </c>
@@ -15620,7 +15641,7 @@
         <v>467</v>
       </c>
     </row>
-    <row r="97" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="97" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A97" t="s">
         <v>18</v>
       </c>
@@ -15664,7 +15685,7 @@
         <v>472</v>
       </c>
     </row>
-    <row r="98" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="98" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A98" t="s">
         <v>18</v>
       </c>
@@ -15708,7 +15729,7 @@
         <v>476</v>
       </c>
     </row>
-    <row r="99" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="99" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A99" t="s">
         <v>18</v>
       </c>
@@ -15752,7 +15773,7 @@
         <v>481</v>
       </c>
     </row>
-    <row r="100" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="100" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A100" t="s">
         <v>18</v>
       </c>
@@ -15796,7 +15817,7 @@
         <v>485</v>
       </c>
     </row>
-    <row r="101" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="101" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A101" t="s">
         <v>18</v>
       </c>
@@ -15840,7 +15861,7 @@
         <v>490</v>
       </c>
     </row>
-    <row r="102" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="102" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A102" t="s">
         <v>18</v>
       </c>
@@ -15884,7 +15905,7 @@
         <v>492</v>
       </c>
     </row>
-    <row r="103" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="103" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A103" t="s">
         <v>18</v>
       </c>
@@ -15928,7 +15949,7 @@
         <v>496</v>
       </c>
     </row>
-    <row r="104" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="104" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A104" t="s">
         <v>18</v>
       </c>
@@ -15972,7 +15993,7 @@
         <v>501</v>
       </c>
     </row>
-    <row r="105" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="105" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A105" t="s">
         <v>18</v>
       </c>
@@ -16016,7 +16037,7 @@
         <v>506</v>
       </c>
     </row>
-    <row r="106" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="106" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A106" t="s">
         <v>18</v>
       </c>
@@ -16060,7 +16081,7 @@
         <v>510</v>
       </c>
     </row>
-    <row r="107" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="107" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A107" t="s">
         <v>18</v>
       </c>
@@ -16104,7 +16125,7 @@
         <v>515</v>
       </c>
     </row>
-    <row r="108" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="108" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A108" t="s">
         <v>18</v>
       </c>
@@ -16148,7 +16169,7 @@
         <v>517</v>
       </c>
     </row>
-    <row r="109" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="109" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A109" t="s">
         <v>18</v>
       </c>
@@ -16192,7 +16213,7 @@
         <v>521</v>
       </c>
     </row>
-    <row r="110" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="110" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A110" t="s">
         <v>18</v>
       </c>
@@ -16236,7 +16257,7 @@
         <v>523</v>
       </c>
     </row>
-    <row r="111" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="111" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A111" t="s">
         <v>18</v>
       </c>
@@ -16280,7 +16301,7 @@
         <v>527</v>
       </c>
     </row>
-    <row r="112" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="112" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A112" t="s">
         <v>18</v>
       </c>
@@ -16324,7 +16345,7 @@
         <v>532</v>
       </c>
     </row>
-    <row r="113" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="113" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A113" t="s">
         <v>18</v>
       </c>
@@ -16368,7 +16389,7 @@
         <v>537</v>
       </c>
     </row>
-    <row r="114" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="114" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A114" t="s">
         <v>18</v>
       </c>
@@ -16412,7 +16433,7 @@
         <v>541</v>
       </c>
     </row>
-    <row r="115" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="115" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A115" t="s">
         <v>18</v>
       </c>
@@ -16456,7 +16477,7 @@
         <v>546</v>
       </c>
     </row>
-    <row r="116" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="116" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A116" t="s">
         <v>18</v>
       </c>
@@ -16500,7 +16521,7 @@
         <v>550</v>
       </c>
     </row>
-    <row r="117" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="117" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A117" t="s">
         <v>18</v>
       </c>
@@ -16544,7 +16565,7 @@
         <v>552</v>
       </c>
     </row>
-    <row r="118" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="118" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A118" t="s">
         <v>18</v>
       </c>
@@ -16588,7 +16609,7 @@
         <v>554</v>
       </c>
     </row>
-    <row r="119" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="119" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A119" t="s">
         <v>18</v>
       </c>
@@ -16632,7 +16653,7 @@
         <v>558</v>
       </c>
     </row>
-    <row r="120" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="120" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A120" t="s">
         <v>18</v>
       </c>
@@ -16676,7 +16697,7 @@
         <v>560</v>
       </c>
     </row>
-    <row r="121" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="121" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A121" t="s">
         <v>18</v>
       </c>
@@ -16720,7 +16741,7 @@
         <v>564</v>
       </c>
     </row>
-    <row r="122" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="122" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A122" t="s">
         <v>18</v>
       </c>
@@ -16764,7 +16785,7 @@
         <v>569</v>
       </c>
     </row>
-    <row r="123" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="123" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A123" t="s">
         <v>18</v>
       </c>
@@ -16808,7 +16829,7 @@
         <v>573</v>
       </c>
     </row>
-    <row r="124" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="124" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A124" t="s">
         <v>18</v>
       </c>
@@ -16852,7 +16873,7 @@
         <v>577</v>
       </c>
     </row>
-    <row r="125" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="125" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A125" t="s">
         <v>18</v>
       </c>
@@ -16893,7 +16914,7 @@
         <v>578</v>
       </c>
     </row>
-    <row r="126" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="126" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A126" t="s">
         <v>18</v>
       </c>
@@ -16937,7 +16958,7 @@
         <v>580</v>
       </c>
     </row>
-    <row r="127" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="127" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A127" t="s">
         <v>18</v>
       </c>
@@ -16981,7 +17002,7 @@
         <v>581</v>
       </c>
     </row>
-    <row r="128" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="128" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A128" t="s">
         <v>18</v>
       </c>
@@ -17025,7 +17046,7 @@
         <v>582</v>
       </c>
     </row>
-    <row r="129" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="129" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A129" t="s">
         <v>18</v>
       </c>
@@ -17069,7 +17090,7 @@
         <v>588</v>
       </c>
     </row>
-    <row r="130" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="130" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A130" t="s">
         <v>18</v>
       </c>
@@ -17113,7 +17134,7 @@
         <v>591</v>
       </c>
     </row>
-    <row r="131" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="131" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A131" t="s">
         <v>18</v>
       </c>
@@ -17157,7 +17178,7 @@
         <v>595</v>
       </c>
     </row>
-    <row r="132" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="132" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A132" t="s">
         <v>18</v>
       </c>
@@ -17201,7 +17222,7 @@
         <v>596</v>
       </c>
     </row>
-    <row r="133" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="133" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A133" t="s">
         <v>18</v>
       </c>
@@ -17245,7 +17266,7 @@
         <v>599</v>
       </c>
     </row>
-    <row r="134" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="134" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A134" t="s">
         <v>18</v>
       </c>
@@ -17289,7 +17310,7 @@
         <v>603</v>
       </c>
     </row>
-    <row r="135" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="135" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A135" t="s">
         <v>18</v>
       </c>
@@ -17333,7 +17354,7 @@
         <v>607</v>
       </c>
     </row>
-    <row r="136" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="136" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A136" t="s">
         <v>18</v>
       </c>
@@ -17377,7 +17398,7 @@
         <v>611</v>
       </c>
     </row>
-    <row r="137" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="137" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A137" t="s">
         <v>18</v>
       </c>
@@ -17421,7 +17442,7 @@
         <v>616</v>
       </c>
     </row>
-    <row r="138" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="138" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A138" t="s">
         <v>18</v>
       </c>
@@ -17465,7 +17486,7 @@
         <v>621</v>
       </c>
     </row>
-    <row r="139" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="139" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A139" t="s">
         <v>18</v>
       </c>
@@ -17509,7 +17530,7 @@
         <v>626</v>
       </c>
     </row>
-    <row r="140" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="140" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A140" t="s">
         <v>18</v>
       </c>
@@ -17553,7 +17574,7 @@
         <v>630</v>
       </c>
     </row>
-    <row r="141" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="141" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A141" t="s">
         <v>18</v>
       </c>
@@ -17597,7 +17618,7 @@
         <v>631</v>
       </c>
     </row>
-    <row r="142" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="142" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A142" t="s">
         <v>18</v>
       </c>
@@ -17641,7 +17662,7 @@
         <v>635</v>
       </c>
     </row>
-    <row r="143" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="143" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A143" t="s">
         <v>18</v>
       </c>
@@ -17685,7 +17706,7 @@
         <v>640</v>
       </c>
     </row>
-    <row r="144" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="144" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A144" t="s">
         <v>18</v>
       </c>
@@ -17729,7 +17750,7 @@
         <v>646</v>
       </c>
     </row>
-    <row r="145" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="145" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A145" t="s">
         <v>18</v>
       </c>
@@ -17817,7 +17838,7 @@
         <v>655</v>
       </c>
     </row>
-    <row r="147" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="147" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A147" t="s">
         <v>18</v>
       </c>
@@ -17861,7 +17882,7 @@
         <v>659</v>
       </c>
     </row>
-    <row r="148" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="148" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A148" t="s">
         <v>18</v>
       </c>
@@ -17905,7 +17926,7 @@
         <v>661</v>
       </c>
     </row>
-    <row r="149" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="149" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A149" t="s">
         <v>18</v>
       </c>
@@ -17949,7 +17970,7 @@
         <v>665</v>
       </c>
     </row>
-    <row r="150" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="150" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A150" t="s">
         <v>18</v>
       </c>
@@ -17993,7 +18014,7 @@
         <v>669</v>
       </c>
     </row>
-    <row r="151" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="151" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A151" t="s">
         <v>18</v>
       </c>
@@ -18037,7 +18058,7 @@
         <v>673</v>
       </c>
     </row>
-    <row r="152" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="152" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A152" t="s">
         <v>18</v>
       </c>
@@ -18081,7 +18102,7 @@
         <v>678</v>
       </c>
     </row>
-    <row r="153" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="153" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A153" t="s">
         <v>18</v>
       </c>
@@ -18125,7 +18146,7 @@
         <v>683</v>
       </c>
     </row>
-    <row r="154" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="154" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A154" t="s">
         <v>18</v>
       </c>
@@ -18169,7 +18190,7 @@
         <v>687</v>
       </c>
     </row>
-    <row r="155" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="155" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A155" t="s">
         <v>18</v>
       </c>
@@ -18213,7 +18234,7 @@
         <v>692</v>
       </c>
     </row>
-    <row r="156" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="156" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A156" t="s">
         <v>18</v>
       </c>
@@ -18257,7 +18278,7 @@
         <v>697</v>
       </c>
     </row>
-    <row r="157" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="157" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A157" t="s">
         <v>18</v>
       </c>
@@ -18301,7 +18322,7 @@
         <v>702</v>
       </c>
     </row>
-    <row r="158" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="158" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A158" t="s">
         <v>18</v>
       </c>
@@ -18345,7 +18366,7 @@
         <v>704</v>
       </c>
     </row>
-    <row r="159" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="159" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A159" t="s">
         <v>18</v>
       </c>
@@ -18389,7 +18410,7 @@
         <v>708</v>
       </c>
     </row>
-    <row r="160" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="160" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A160" t="s">
         <v>18</v>
       </c>
@@ -18433,7 +18454,7 @@
         <v>712</v>
       </c>
     </row>
-    <row r="161" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="161" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A161" t="s">
         <v>18</v>
       </c>
@@ -18477,7 +18498,7 @@
         <v>713</v>
       </c>
     </row>
-    <row r="162" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="162" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A162" t="s">
         <v>18</v>
       </c>
@@ -18521,7 +18542,7 @@
         <v>717</v>
       </c>
     </row>
-    <row r="163" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="163" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A163" t="s">
         <v>18</v>
       </c>
@@ -18565,7 +18586,7 @@
         <v>722</v>
       </c>
     </row>
-    <row r="164" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="164" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A164" t="s">
         <v>18</v>
       </c>
@@ -18609,7 +18630,7 @@
         <v>727</v>
       </c>
     </row>
-    <row r="165" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="165" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A165" t="s">
         <v>18</v>
       </c>
@@ -18653,7 +18674,7 @@
         <v>731</v>
       </c>
     </row>
-    <row r="166" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="166" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A166" t="s">
         <v>18</v>
       </c>
@@ -18697,7 +18718,7 @@
         <v>735</v>
       </c>
     </row>
-    <row r="167" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="167" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A167" t="s">
         <v>18</v>
       </c>
@@ -18741,7 +18762,7 @@
         <v>739</v>
       </c>
     </row>
-    <row r="168" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="168" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A168" t="s">
         <v>18</v>
       </c>
@@ -18829,7 +18850,7 @@
         <v>747</v>
       </c>
     </row>
-    <row r="170" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="170" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A170" t="s">
         <v>18</v>
       </c>
@@ -18873,7 +18894,7 @@
         <v>752</v>
       </c>
     </row>
-    <row r="171" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="171" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A171" t="s">
         <v>18</v>
       </c>
@@ -18917,7 +18938,7 @@
         <v>754</v>
       </c>
     </row>
-    <row r="172" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="172" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A172" t="s">
         <v>18</v>
       </c>
@@ -18961,7 +18982,7 @@
         <v>756</v>
       </c>
     </row>
-    <row r="173" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="173" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A173" t="s">
         <v>18</v>
       </c>
@@ -19225,7 +19246,7 @@
         <v>785</v>
       </c>
     </row>
-    <row r="179" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="179" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A179" t="s">
         <v>18</v>
       </c>
@@ -19269,7 +19290,7 @@
         <v>790</v>
       </c>
     </row>
-    <row r="180" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="180" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A180" t="s">
         <v>18</v>
       </c>
@@ -19313,7 +19334,7 @@
         <v>794</v>
       </c>
     </row>
-    <row r="181" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="181" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A181" t="s">
         <v>18</v>
       </c>
@@ -19357,7 +19378,7 @@
         <v>799</v>
       </c>
     </row>
-    <row r="182" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="182" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A182" t="s">
         <v>18</v>
       </c>
@@ -19401,7 +19422,7 @@
         <v>803</v>
       </c>
     </row>
-    <row r="183" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="183" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A183" t="s">
         <v>18</v>
       </c>
@@ -19445,7 +19466,7 @@
         <v>808</v>
       </c>
     </row>
-    <row r="184" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="184" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A184" t="s">
         <v>18</v>
       </c>
@@ -19489,7 +19510,7 @@
         <v>813</v>
       </c>
     </row>
-    <row r="185" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="185" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A185" t="s">
         <v>18</v>
       </c>
@@ -19533,7 +19554,7 @@
         <v>817</v>
       </c>
     </row>
-    <row r="186" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="186" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A186" t="s">
         <v>18</v>
       </c>
@@ -19577,7 +19598,7 @@
         <v>822</v>
       </c>
     </row>
-    <row r="187" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="187" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A187" t="s">
         <v>18</v>
       </c>
@@ -19621,7 +19642,7 @@
         <v>827</v>
       </c>
     </row>
-    <row r="188" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="188" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A188" t="s">
         <v>18</v>
       </c>
@@ -19665,7 +19686,7 @@
         <v>831</v>
       </c>
     </row>
-    <row r="189" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="189" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A189" t="s">
         <v>18</v>
       </c>
@@ -19709,7 +19730,7 @@
         <v>836</v>
       </c>
     </row>
-    <row r="190" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="190" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A190" t="s">
         <v>18</v>
       </c>
@@ -19753,7 +19774,7 @@
         <v>838</v>
       </c>
     </row>
-    <row r="191" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="191" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A191" t="s">
         <v>18</v>
       </c>
@@ -19797,7 +19818,7 @@
         <v>840</v>
       </c>
     </row>
-    <row r="192" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="192" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A192" t="s">
         <v>18</v>
       </c>
@@ -19838,7 +19859,7 @@
         <v>843</v>
       </c>
     </row>
-    <row r="193" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="193" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A193" t="s">
         <v>18</v>
       </c>
@@ -19926,7 +19947,7 @@
         <v>853</v>
       </c>
     </row>
-    <row r="195" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="195" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A195" t="s">
         <v>18</v>
       </c>
@@ -19970,7 +19991,7 @@
         <v>858</v>
       </c>
     </row>
-    <row r="196" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="196" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A196" t="s">
         <v>18</v>
       </c>
@@ -20011,7 +20032,7 @@
         <v>862</v>
       </c>
     </row>
-    <row r="197" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="197" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A197" t="s">
         <v>18</v>
       </c>
@@ -20055,7 +20076,7 @@
         <v>867</v>
       </c>
     </row>
-    <row r="198" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="198" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A198" t="s">
         <v>18</v>
       </c>
@@ -20099,7 +20120,7 @@
         <v>871</v>
       </c>
     </row>
-    <row r="199" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="199" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A199" t="s">
         <v>18</v>
       </c>
@@ -20143,7 +20164,7 @@
         <v>873</v>
       </c>
     </row>
-    <row r="200" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="200" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A200" t="s">
         <v>18</v>
       </c>
@@ -20187,7 +20208,7 @@
         <v>877</v>
       </c>
     </row>
-    <row r="201" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="201" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A201" t="s">
         <v>18</v>
       </c>
@@ -20231,7 +20252,7 @@
         <v>882</v>
       </c>
     </row>
-    <row r="202" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="202" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A202" t="s">
         <v>18</v>
       </c>
@@ -20275,7 +20296,7 @@
         <v>886</v>
       </c>
     </row>
-    <row r="203" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="203" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A203" t="s">
         <v>18</v>
       </c>
@@ -20319,7 +20340,7 @@
         <v>890</v>
       </c>
     </row>
-    <row r="204" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="204" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A204" t="s">
         <v>18</v>
       </c>
@@ -20363,7 +20384,7 @@
         <v>894</v>
       </c>
     </row>
-    <row r="205" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="205" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A205" t="s">
         <v>18</v>
       </c>
@@ -20407,7 +20428,7 @@
         <v>898</v>
       </c>
     </row>
-    <row r="206" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="206" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A206" t="s">
         <v>18</v>
       </c>
@@ -20451,7 +20472,7 @@
         <v>903</v>
       </c>
     </row>
-    <row r="207" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="207" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A207" t="s">
         <v>18</v>
       </c>
@@ -20539,7 +20560,7 @@
         <v>909</v>
       </c>
     </row>
-    <row r="209" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="209" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A209" t="s">
         <v>18</v>
       </c>
@@ -20583,7 +20604,7 @@
         <v>913</v>
       </c>
     </row>
-    <row r="210" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="210" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A210" t="s">
         <v>18</v>
       </c>
@@ -20627,7 +20648,7 @@
         <v>918</v>
       </c>
     </row>
-    <row r="211" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="211" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A211" t="s">
         <v>18</v>
       </c>
@@ -20671,7 +20692,7 @@
         <v>923</v>
       </c>
     </row>
-    <row r="212" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="212" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A212" t="s">
         <v>18</v>
       </c>
@@ -20715,7 +20736,7 @@
         <v>927</v>
       </c>
     </row>
-    <row r="213" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="213" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A213" t="s">
         <v>18</v>
       </c>
@@ -20759,7 +20780,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="214" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="214" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A214" t="s">
         <v>18</v>
       </c>
@@ -20803,7 +20824,7 @@
         <v>931</v>
       </c>
     </row>
-    <row r="215" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="215" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A215" t="s">
         <v>18</v>
       </c>
@@ -20847,7 +20868,7 @@
         <v>936</v>
       </c>
     </row>
-    <row r="216" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="216" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A216" t="s">
         <v>18</v>
       </c>
@@ -20891,7 +20912,7 @@
         <v>939</v>
       </c>
     </row>
-    <row r="217" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="217" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A217" t="s">
         <v>18</v>
       </c>
@@ -20935,7 +20956,7 @@
         <v>943</v>
       </c>
     </row>
-    <row r="218" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="218" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A218" t="s">
         <v>18</v>
       </c>
@@ -20979,7 +21000,7 @@
         <v>945</v>
       </c>
     </row>
-    <row r="219" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="219" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A219" t="s">
         <v>18</v>
       </c>
@@ -21023,7 +21044,7 @@
         <v>950</v>
       </c>
     </row>
-    <row r="220" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="220" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A220" t="s">
         <v>18</v>
       </c>
@@ -21067,7 +21088,7 @@
         <v>954</v>
       </c>
     </row>
-    <row r="221" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="221" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A221" t="s">
         <v>18</v>
       </c>
@@ -21111,7 +21132,7 @@
         <v>958</v>
       </c>
     </row>
-    <row r="222" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="222" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A222" t="s">
         <v>18</v>
       </c>
@@ -21152,7 +21173,7 @@
         <v>959</v>
       </c>
     </row>
-    <row r="223" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="223" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A223" t="s">
         <v>18</v>
       </c>
@@ -21196,7 +21217,7 @@
         <v>961</v>
       </c>
     </row>
-    <row r="224" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="224" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A224" t="s">
         <v>18</v>
       </c>
@@ -21240,7 +21261,7 @@
         <v>965</v>
       </c>
     </row>
-    <row r="225" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="225" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A225" t="s">
         <v>18</v>
       </c>
@@ -21284,7 +21305,7 @@
         <v>969</v>
       </c>
     </row>
-    <row r="226" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="226" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A226" t="s">
         <v>18</v>
       </c>
@@ -21372,7 +21393,7 @@
         <v>977</v>
       </c>
     </row>
-    <row r="228" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="228" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A228" t="s">
         <v>18</v>
       </c>
@@ -21413,7 +21434,7 @@
         <v>981</v>
       </c>
     </row>
-    <row r="229" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="229" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A229" t="s">
         <v>18</v>
       </c>
@@ -21457,7 +21478,7 @@
         <v>985</v>
       </c>
     </row>
-    <row r="230" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="230" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A230" t="s">
         <v>18</v>
       </c>
@@ -21501,7 +21522,7 @@
         <v>987</v>
       </c>
     </row>
-    <row r="231" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="231" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A231" t="s">
         <v>18</v>
       </c>
@@ -21545,7 +21566,7 @@
         <v>991</v>
       </c>
     </row>
-    <row r="232" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="232" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A232" t="s">
         <v>18</v>
       </c>
@@ -21589,7 +21610,7 @@
         <v>995</v>
       </c>
     </row>
-    <row r="233" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="233" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A233" t="s">
         <v>18</v>
       </c>
@@ -21633,7 +21654,7 @@
         <v>999</v>
       </c>
     </row>
-    <row r="234" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="234" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A234" t="s">
         <v>18</v>
       </c>
@@ -21677,7 +21698,7 @@
         <v>1003</v>
       </c>
     </row>
-    <row r="235" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="235" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A235" t="s">
         <v>18</v>
       </c>
@@ -21721,7 +21742,7 @@
         <v>1007</v>
       </c>
     </row>
-    <row r="236" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="236" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A236" t="s">
         <v>18</v>
       </c>
@@ -21765,7 +21786,7 @@
         <v>1012</v>
       </c>
     </row>
-    <row r="237" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="237" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A237" t="s">
         <v>18</v>
       </c>
@@ -21809,7 +21830,7 @@
         <v>1014</v>
       </c>
     </row>
-    <row r="238" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="238" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A238" t="s">
         <v>18</v>
       </c>
@@ -21853,7 +21874,7 @@
         <v>1016</v>
       </c>
     </row>
-    <row r="239" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="239" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A239" t="s">
         <v>18</v>
       </c>
@@ -21897,7 +21918,7 @@
         <v>1020</v>
       </c>
     </row>
-    <row r="240" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="240" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A240" t="s">
         <v>18</v>
       </c>
@@ -21941,7 +21962,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="241" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="241" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A241" t="s">
         <v>18</v>
       </c>
@@ -21985,7 +22006,7 @@
         <v>1029</v>
       </c>
     </row>
-    <row r="242" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="242" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A242" t="s">
         <v>18</v>
       </c>
@@ -22029,7 +22050,7 @@
         <v>1034</v>
       </c>
     </row>
-    <row r="243" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="243" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A243" t="s">
         <v>18</v>
       </c>
@@ -22073,7 +22094,7 @@
         <v>1038</v>
       </c>
     </row>
-    <row r="244" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="244" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A244" t="s">
         <v>18</v>
       </c>
@@ -22117,7 +22138,7 @@
         <v>1043</v>
       </c>
     </row>
-    <row r="245" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="245" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A245" t="s">
         <v>18</v>
       </c>
@@ -22161,7 +22182,7 @@
         <v>1047</v>
       </c>
     </row>
-    <row r="246" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="246" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A246" t="s">
         <v>18</v>
       </c>
@@ -22205,7 +22226,7 @@
         <v>1051</v>
       </c>
     </row>
-    <row r="247" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="247" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A247" t="s">
         <v>18</v>
       </c>
@@ -22249,7 +22270,7 @@
         <v>1055</v>
       </c>
     </row>
-    <row r="248" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="248" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A248" t="s">
         <v>18</v>
       </c>
@@ -22293,7 +22314,7 @@
         <v>1059</v>
       </c>
     </row>
-    <row r="249" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="249" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A249" t="s">
         <v>18</v>
       </c>
@@ -22337,7 +22358,7 @@
         <v>1064</v>
       </c>
     </row>
-    <row r="250" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="250" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A250" t="s">
         <v>18</v>
       </c>
@@ -22381,7 +22402,7 @@
         <v>1069</v>
       </c>
     </row>
-    <row r="251" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="251" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A251" t="s">
         <v>18</v>
       </c>
@@ -22425,7 +22446,7 @@
         <v>1074</v>
       </c>
     </row>
-    <row r="252" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="252" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A252" t="s">
         <v>18</v>
       </c>
@@ -22469,7 +22490,7 @@
         <v>1079</v>
       </c>
     </row>
-    <row r="253" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="253" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A253" t="s">
         <v>18</v>
       </c>
@@ -22513,7 +22534,7 @@
         <v>1084</v>
       </c>
     </row>
-    <row r="254" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="254" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A254" t="s">
         <v>18</v>
       </c>
@@ -22777,7 +22798,7 @@
         <v>1107</v>
       </c>
     </row>
-    <row r="260" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="260" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A260" t="s">
         <v>18</v>
       </c>
@@ -22821,7 +22842,7 @@
         <v>1111</v>
       </c>
     </row>
-    <row r="261" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="261" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A261" t="s">
         <v>18</v>
       </c>
@@ -23085,7 +23106,7 @@
         <v>1137</v>
       </c>
     </row>
-    <row r="267" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="267" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A267" t="s">
         <v>18</v>
       </c>
@@ -23129,7 +23150,7 @@
         <v>1141</v>
       </c>
     </row>
-    <row r="268" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="268" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A268" t="s">
         <v>18</v>
       </c>
@@ -23173,7 +23194,7 @@
         <v>1143</v>
       </c>
     </row>
-    <row r="269" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="269" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A269" t="s">
         <v>18</v>
       </c>
@@ -23217,7 +23238,7 @@
         <v>1149</v>
       </c>
     </row>
-    <row r="270" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="270" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A270" t="s">
         <v>18</v>
       </c>
@@ -23258,7 +23279,7 @@
         <v>1153</v>
       </c>
     </row>
-    <row r="271" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="271" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A271" t="s">
         <v>18</v>
       </c>
@@ -23302,7 +23323,7 @@
         <v>1157</v>
       </c>
     </row>
-    <row r="272" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="272" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A272" t="s">
         <v>18</v>
       </c>
@@ -23346,7 +23367,7 @@
         <v>1161</v>
       </c>
     </row>
-    <row r="273" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="273" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A273" t="s">
         <v>18</v>
       </c>
@@ -23390,7 +23411,7 @@
         <v>1164</v>
       </c>
     </row>
-    <row r="274" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="274" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A274" t="s">
         <v>18</v>
       </c>
@@ -23434,7 +23455,7 @@
         <v>1166</v>
       </c>
     </row>
-    <row r="275" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="275" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A275" t="s">
         <v>18</v>
       </c>
@@ -23522,7 +23543,7 @@
         <v>1175</v>
       </c>
     </row>
-    <row r="277" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="277" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A277" t="s">
         <v>18</v>
       </c>
@@ -23563,7 +23584,7 @@
         <v>1180</v>
       </c>
     </row>
-    <row r="278" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="278" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A278" t="s">
         <v>18</v>
       </c>
@@ -23607,7 +23628,7 @@
         <v>1184</v>
       </c>
     </row>
-    <row r="279" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="279" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A279" t="s">
         <v>18</v>
       </c>
@@ -23651,7 +23672,7 @@
         <v>1189</v>
       </c>
     </row>
-    <row r="280" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="280" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A280" t="s">
         <v>18</v>
       </c>
@@ -23695,7 +23716,7 @@
         <v>1192</v>
       </c>
     </row>
-    <row r="281" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="281" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A281" t="s">
         <v>18</v>
       </c>
@@ -23739,7 +23760,7 @@
         <v>1196</v>
       </c>
     </row>
-    <row r="282" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="282" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A282" t="s">
         <v>18</v>
       </c>
@@ -23783,7 +23804,7 @@
         <v>1200</v>
       </c>
     </row>
-    <row r="283" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="283" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A283" t="s">
         <v>18</v>
       </c>
@@ -23827,7 +23848,7 @@
         <v>1204</v>
       </c>
     </row>
-    <row r="284" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="284" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A284" t="s">
         <v>18</v>
       </c>
@@ -23915,7 +23936,7 @@
         <v>1214</v>
       </c>
     </row>
-    <row r="286" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="286" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A286" t="s">
         <v>18</v>
       </c>
@@ -23959,7 +23980,7 @@
         <v>1219</v>
       </c>
     </row>
-    <row r="287" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="287" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A287" t="s">
         <v>18</v>
       </c>
@@ -24003,7 +24024,7 @@
         <v>1223</v>
       </c>
     </row>
-    <row r="288" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="288" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A288" t="s">
         <v>18</v>
       </c>
@@ -24091,7 +24112,7 @@
         <v>1233</v>
       </c>
     </row>
-    <row r="290" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="290" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A290" t="s">
         <v>18</v>
       </c>
@@ -24135,7 +24156,7 @@
         <v>1237</v>
       </c>
     </row>
-    <row r="291" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="291" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A291" t="s">
         <v>18</v>
       </c>
@@ -24179,7 +24200,7 @@
         <v>1241</v>
       </c>
     </row>
-    <row r="292" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="292" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A292" t="s">
         <v>18</v>
       </c>
@@ -24223,7 +24244,7 @@
         <v>1246</v>
       </c>
     </row>
-    <row r="293" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="293" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A293" t="s">
         <v>18</v>
       </c>
@@ -24267,7 +24288,7 @@
         <v>1250</v>
       </c>
     </row>
-    <row r="294" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="294" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A294" t="s">
         <v>18</v>
       </c>
@@ -24311,7 +24332,7 @@
         <v>1255</v>
       </c>
     </row>
-    <row r="295" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="295" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A295" t="s">
         <v>18</v>
       </c>
@@ -24355,7 +24376,7 @@
         <v>1259</v>
       </c>
     </row>
-    <row r="296" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="296" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A296" t="s">
         <v>18</v>
       </c>
@@ -24399,7 +24420,7 @@
         <v>1263</v>
       </c>
     </row>
-    <row r="297" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="297" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A297" t="s">
         <v>18</v>
       </c>
@@ -24443,7 +24464,7 @@
         <v>1268</v>
       </c>
     </row>
-    <row r="298" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="298" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A298" t="s">
         <v>18</v>
       </c>
@@ -24487,7 +24508,7 @@
         <v>1273</v>
       </c>
     </row>
-    <row r="299" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="299" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A299" t="s">
         <v>18</v>
       </c>
@@ -24531,7 +24552,7 @@
         <v>1277</v>
       </c>
     </row>
-    <row r="300" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="300" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A300" t="s">
         <v>18</v>
       </c>
@@ -24575,7 +24596,7 @@
         <v>1281</v>
       </c>
     </row>
-    <row r="301" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="301" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A301" t="s">
         <v>18</v>
       </c>
@@ -24663,7 +24684,7 @@
         <v>1289</v>
       </c>
     </row>
-    <row r="303" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="303" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A303" t="s">
         <v>18</v>
       </c>
@@ -24751,7 +24772,7 @@
         <v>1299</v>
       </c>
     </row>
-    <row r="305" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="305" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A305" t="s">
         <v>18</v>
       </c>
@@ -24795,7 +24816,7 @@
         <v>1304</v>
       </c>
     </row>
-    <row r="306" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="306" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A306" t="s">
         <v>18</v>
       </c>
@@ -24839,7 +24860,7 @@
         <v>1308</v>
       </c>
     </row>
-    <row r="307" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="307" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A307" t="s">
         <v>18</v>
       </c>
@@ -24883,7 +24904,7 @@
         <v>1312</v>
       </c>
     </row>
-    <row r="308" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="308" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A308" t="s">
         <v>18</v>
       </c>
@@ -24927,7 +24948,7 @@
         <v>1316</v>
       </c>
     </row>
-    <row r="309" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="309" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A309" t="s">
         <v>18</v>
       </c>
@@ -24971,7 +24992,7 @@
         <v>1317</v>
       </c>
     </row>
-    <row r="310" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="310" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A310" t="s">
         <v>18</v>
       </c>
@@ -25015,7 +25036,7 @@
         <v>1318</v>
       </c>
     </row>
-    <row r="311" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="311" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A311" t="s">
         <v>18</v>
       </c>
@@ -25059,7 +25080,7 @@
         <v>1319</v>
       </c>
     </row>
-    <row r="312" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="312" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A312" t="s">
         <v>18</v>
       </c>
@@ -25103,7 +25124,7 @@
         <v>1323</v>
       </c>
     </row>
-    <row r="313" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="313" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A313" t="s">
         <v>18</v>
       </c>
@@ -25147,7 +25168,7 @@
         <v>1328</v>
       </c>
     </row>
-    <row r="314" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="314" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A314" t="s">
         <v>18</v>
       </c>
@@ -25235,7 +25256,7 @@
         <v>1334</v>
       </c>
     </row>
-    <row r="316" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="316" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A316" t="s">
         <v>18</v>
       </c>
@@ -25279,7 +25300,7 @@
         <v>1339</v>
       </c>
     </row>
-    <row r="317" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="317" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A317" t="s">
         <v>18</v>
       </c>
@@ -25323,7 +25344,7 @@
         <v>1344</v>
       </c>
     </row>
-    <row r="318" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="318" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A318" t="s">
         <v>18</v>
       </c>
@@ -25367,7 +25388,7 @@
         <v>1346</v>
       </c>
     </row>
-    <row r="319" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="319" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A319" t="s">
         <v>18</v>
       </c>
@@ -25411,7 +25432,7 @@
         <v>1348</v>
       </c>
     </row>
-    <row r="320" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="320" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A320" t="s">
         <v>18</v>
       </c>
@@ -25455,7 +25476,7 @@
         <v>1353</v>
       </c>
     </row>
-    <row r="321" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="321" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A321" t="s">
         <v>18</v>
       </c>
@@ -25499,7 +25520,7 @@
         <v>1358</v>
       </c>
     </row>
-    <row r="322" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="322" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A322" t="s">
         <v>18</v>
       </c>
@@ -25543,7 +25564,7 @@
         <v>1362</v>
       </c>
     </row>
-    <row r="323" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="323" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A323" t="s">
         <v>18</v>
       </c>
@@ -25587,7 +25608,7 @@
         <v>1366</v>
       </c>
     </row>
-    <row r="324" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="324" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A324" t="s">
         <v>18</v>
       </c>
@@ -25631,7 +25652,7 @@
         <v>1371</v>
       </c>
     </row>
-    <row r="325" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="325" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A325" t="s">
         <v>18</v>
       </c>
@@ -25675,7 +25696,7 @@
         <v>1376</v>
       </c>
     </row>
-    <row r="326" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="326" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A326" t="s">
         <v>18</v>
       </c>
@@ -25719,7 +25740,7 @@
         <v>1380</v>
       </c>
     </row>
-    <row r="327" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="327" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A327" t="s">
         <v>18</v>
       </c>
@@ -25763,7 +25784,7 @@
         <v>1384</v>
       </c>
     </row>
-    <row r="328" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="328" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A328" t="s">
         <v>18</v>
       </c>
@@ -25807,7 +25828,7 @@
         <v>1388</v>
       </c>
     </row>
-    <row r="329" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="329" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A329" t="s">
         <v>18</v>
       </c>
@@ -25851,7 +25872,7 @@
         <v>1392</v>
       </c>
     </row>
-    <row r="330" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="330" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A330" t="s">
         <v>18</v>
       </c>
@@ -25895,7 +25916,7 @@
         <v>1397</v>
       </c>
     </row>
-    <row r="331" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="331" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A331" t="s">
         <v>18</v>
       </c>
@@ -25939,7 +25960,7 @@
         <v>1401</v>
       </c>
     </row>
-    <row r="332" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="332" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A332" t="s">
         <v>18</v>
       </c>
@@ -25980,7 +26001,7 @@
         <v>1404</v>
       </c>
     </row>
-    <row r="333" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="333" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A333" t="s">
         <v>18</v>
       </c>
@@ -26024,7 +26045,7 @@
         <v>1408</v>
       </c>
     </row>
-    <row r="334" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="334" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A334" t="s">
         <v>18</v>
       </c>
@@ -26068,7 +26089,7 @@
         <v>1410</v>
       </c>
     </row>
-    <row r="335" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="335" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A335" t="s">
         <v>18</v>
       </c>
@@ -26112,7 +26133,7 @@
         <v>1412</v>
       </c>
     </row>
-    <row r="336" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="336" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A336" t="s">
         <v>18</v>
       </c>
@@ -26156,7 +26177,7 @@
         <v>1417</v>
       </c>
     </row>
-    <row r="337" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="337" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A337" t="s">
         <v>18</v>
       </c>
@@ -26200,7 +26221,7 @@
         <v>1421</v>
       </c>
     </row>
-    <row r="338" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="338" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A338" t="s">
         <v>18</v>
       </c>
@@ -26244,7 +26265,7 @@
         <v>1426</v>
       </c>
     </row>
-    <row r="339" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="339" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A339" t="s">
         <v>18</v>
       </c>
@@ -26332,7 +26353,7 @@
         <v>1435</v>
       </c>
     </row>
-    <row r="341" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="341" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A341" t="s">
         <v>18</v>
       </c>
@@ -26420,7 +26441,7 @@
         <v>1444</v>
       </c>
     </row>
-    <row r="343" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="343" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A343" t="s">
         <v>18</v>
       </c>
@@ -26464,7 +26485,7 @@
         <v>1449</v>
       </c>
     </row>
-    <row r="344" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="344" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A344" t="s">
         <v>18</v>
       </c>
@@ -26508,7 +26529,7 @@
         <v>1454</v>
       </c>
     </row>
-    <row r="345" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="345" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A345" t="s">
         <v>18</v>
       </c>
@@ -26552,7 +26573,7 @@
         <v>1459</v>
       </c>
     </row>
-    <row r="346" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="346" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A346" t="s">
         <v>18</v>
       </c>
@@ -26596,7 +26617,7 @@
         <v>1465</v>
       </c>
     </row>
-    <row r="347" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="347" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A347" t="s">
         <v>18</v>
       </c>
@@ -26640,7 +26661,7 @@
         <v>1470</v>
       </c>
     </row>
-    <row r="348" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="348" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A348" t="s">
         <v>18</v>
       </c>
@@ -26684,7 +26705,7 @@
         <v>1474</v>
       </c>
     </row>
-    <row r="349" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="349" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A349" t="s">
         <v>18</v>
       </c>
@@ -26728,7 +26749,7 @@
         <v>1478</v>
       </c>
     </row>
-    <row r="350" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="350" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A350" t="s">
         <v>18</v>
       </c>
@@ -26772,7 +26793,7 @@
         <v>1483</v>
       </c>
     </row>
-    <row r="351" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="351" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A351" t="s">
         <v>18</v>
       </c>
@@ -26816,7 +26837,7 @@
         <v>1487</v>
       </c>
     </row>
-    <row r="352" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="352" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A352" t="s">
         <v>18</v>
       </c>
@@ -26860,7 +26881,7 @@
         <v>1491</v>
       </c>
     </row>
-    <row r="353" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="353" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A353" t="s">
         <v>18</v>
       </c>
@@ -26904,7 +26925,7 @@
         <v>1495</v>
       </c>
     </row>
-    <row r="354" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="354" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A354" t="s">
         <v>18</v>
       </c>
@@ -26948,7 +26969,7 @@
         <v>1499</v>
       </c>
     </row>
-    <row r="355" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="355" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A355" t="s">
         <v>18</v>
       </c>
@@ -26989,7 +27010,7 @@
         <v>1503</v>
       </c>
     </row>
-    <row r="356" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="356" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A356" t="s">
         <v>18</v>
       </c>
@@ -27033,7 +27054,7 @@
         <v>1508</v>
       </c>
     </row>
-    <row r="357" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="357" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A357" t="s">
         <v>18</v>
       </c>
@@ -27077,7 +27098,7 @@
         <v>1512</v>
       </c>
     </row>
-    <row r="358" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="358" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A358" t="s">
         <v>18</v>
       </c>
@@ -27121,7 +27142,7 @@
         <v>1513</v>
       </c>
     </row>
-    <row r="359" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="359" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A359" t="s">
         <v>18</v>
       </c>
@@ -27165,7 +27186,7 @@
         <v>1515</v>
       </c>
     </row>
-    <row r="360" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="360" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A360" t="s">
         <v>18</v>
       </c>
@@ -27209,7 +27230,7 @@
         <v>1517</v>
       </c>
     </row>
-    <row r="361" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="361" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A361" t="s">
         <v>18</v>
       </c>
@@ -27253,7 +27274,7 @@
         <v>1521</v>
       </c>
     </row>
-    <row r="362" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="362" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A362" t="s">
         <v>18</v>
       </c>
@@ -27297,7 +27318,7 @@
         <v>1526</v>
       </c>
     </row>
-    <row r="363" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="363" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A363" t="s">
         <v>18</v>
       </c>
@@ -27341,7 +27362,7 @@
         <v>1530</v>
       </c>
     </row>
-    <row r="364" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="364" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A364" t="s">
         <v>18</v>
       </c>
@@ -27385,7 +27406,7 @@
         <v>1534</v>
       </c>
     </row>
-    <row r="365" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="365" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A365" t="s">
         <v>18</v>
       </c>
@@ -27429,7 +27450,7 @@
         <v>1538</v>
       </c>
     </row>
-    <row r="366" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="366" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A366" t="s">
         <v>18</v>
       </c>
@@ -27561,7 +27582,7 @@
         <v>1549</v>
       </c>
     </row>
-    <row r="369" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="369" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A369" t="s">
         <v>18</v>
       </c>
@@ -27605,7 +27626,7 @@
         <v>1553</v>
       </c>
     </row>
-    <row r="370" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="370" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A370" t="s">
         <v>18</v>
       </c>
@@ -27649,7 +27670,7 @@
         <v>1556</v>
       </c>
     </row>
-    <row r="371" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="371" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A371" t="s">
         <v>18</v>
       </c>
@@ -27693,7 +27714,7 @@
         <v>1561</v>
       </c>
     </row>
-    <row r="372" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="372" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A372" t="s">
         <v>18</v>
       </c>
@@ -27737,7 +27758,7 @@
         <v>1565</v>
       </c>
     </row>
-    <row r="373" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="373" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A373" t="s">
         <v>18</v>
       </c>
@@ -27781,7 +27802,7 @@
         <v>1569</v>
       </c>
     </row>
-    <row r="374" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="374" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A374" t="s">
         <v>18</v>
       </c>
@@ -27825,7 +27846,7 @@
         <v>1573</v>
       </c>
     </row>
-    <row r="375" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="375" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A375" t="s">
         <v>18</v>
       </c>
@@ -27869,7 +27890,7 @@
         <v>1577</v>
       </c>
     </row>
-    <row r="376" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="376" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A376" t="s">
         <v>18</v>
       </c>
@@ -27913,7 +27934,7 @@
         <v>1581</v>
       </c>
     </row>
-    <row r="377" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="377" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A377" t="s">
         <v>18</v>
       </c>
@@ -27957,7 +27978,7 @@
         <v>1585</v>
       </c>
     </row>
-    <row r="378" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="378" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A378" t="s">
         <v>18</v>
       </c>
@@ -28001,7 +28022,7 @@
         <v>1588</v>
       </c>
     </row>
-    <row r="379" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="379" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A379" t="s">
         <v>18</v>
       </c>
@@ -28045,7 +28066,7 @@
         <v>1592</v>
       </c>
     </row>
-    <row r="380" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="380" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A380" t="s">
         <v>18</v>
       </c>
@@ -28174,7 +28195,7 @@
         <v>1604</v>
       </c>
     </row>
-    <row r="383" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="383" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A383" t="s">
         <v>18</v>
       </c>
@@ -28218,7 +28239,7 @@
         <v>1608</v>
       </c>
     </row>
-    <row r="384" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="384" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A384" t="s">
         <v>18</v>
       </c>
@@ -28262,7 +28283,7 @@
         <v>1609</v>
       </c>
     </row>
-    <row r="385" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="385" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A385" t="s">
         <v>18</v>
       </c>
@@ -28306,7 +28327,7 @@
         <v>1613</v>
       </c>
     </row>
-    <row r="386" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="386" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A386" t="s">
         <v>18</v>
       </c>
@@ -28350,7 +28371,7 @@
         <v>1615</v>
       </c>
     </row>
-    <row r="387" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="387" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A387" t="s">
         <v>18</v>
       </c>
@@ -28394,7 +28415,7 @@
         <v>1619</v>
       </c>
     </row>
-    <row r="388" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="388" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A388" t="s">
         <v>18</v>
       </c>
@@ -28438,7 +28459,7 @@
         <v>1623</v>
       </c>
     </row>
-    <row r="389" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="389" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A389" t="s">
         <v>18</v>
       </c>
@@ -28482,7 +28503,7 @@
         <v>1626</v>
       </c>
     </row>
-    <row r="390" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="390" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A390" t="s">
         <v>18</v>
       </c>
@@ -28526,7 +28547,7 @@
         <v>1630</v>
       </c>
     </row>
-    <row r="391" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="391" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A391" t="s">
         <v>18</v>
       </c>
@@ -28570,7 +28591,7 @@
         <v>1635</v>
       </c>
     </row>
-    <row r="392" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="392" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A392" t="s">
         <v>18</v>
       </c>
@@ -28614,7 +28635,7 @@
         <v>1639</v>
       </c>
     </row>
-    <row r="393" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="393" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A393" t="s">
         <v>18</v>
       </c>
@@ -28655,7 +28676,7 @@
         <v>1642</v>
       </c>
     </row>
-    <row r="394" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="394" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A394" t="s">
         <v>18</v>
       </c>
@@ -28699,7 +28720,7 @@
         <v>1645</v>
       </c>
     </row>
-    <row r="395" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="395" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A395" t="s">
         <v>18</v>
       </c>
@@ -28787,7 +28808,7 @@
         <v>1654</v>
       </c>
     </row>
-    <row r="397" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="397" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A397" t="s">
         <v>18</v>
       </c>
@@ -28831,7 +28852,7 @@
         <v>1658</v>
       </c>
     </row>
-    <row r="398" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="398" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A398" t="s">
         <v>18</v>
       </c>
@@ -28875,7 +28896,7 @@
         <v>1660</v>
       </c>
     </row>
-    <row r="399" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="399" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A399" t="s">
         <v>18</v>
       </c>
@@ -28919,7 +28940,7 @@
         <v>1662</v>
       </c>
     </row>
-    <row r="400" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="400" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A400" t="s">
         <v>18</v>
       </c>
@@ -28963,7 +28984,7 @@
         <v>1666</v>
       </c>
     </row>
-    <row r="401" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="401" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A401" t="s">
         <v>18</v>
       </c>
@@ -29007,7 +29028,7 @@
         <v>1670</v>
       </c>
     </row>
-    <row r="402" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="402" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A402" t="s">
         <v>18</v>
       </c>
@@ -29051,7 +29072,7 @@
         <v>1675</v>
       </c>
     </row>
-    <row r="403" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="403" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A403" t="s">
         <v>18</v>
       </c>
@@ -29095,7 +29116,7 @@
         <v>1677</v>
       </c>
     </row>
-    <row r="404" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="404" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A404" t="s">
         <v>18</v>
       </c>
@@ -29139,7 +29160,7 @@
         <v>1682</v>
       </c>
     </row>
-    <row r="405" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="405" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A405" t="s">
         <v>18</v>
       </c>
@@ -29183,7 +29204,7 @@
         <v>1686</v>
       </c>
     </row>
-    <row r="406" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="406" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A406" t="s">
         <v>18</v>
       </c>
@@ -29227,7 +29248,7 @@
         <v>1689</v>
       </c>
     </row>
-    <row r="407" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="407" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A407" t="s">
         <v>18</v>
       </c>
@@ -29271,7 +29292,7 @@
         <v>1692</v>
       </c>
     </row>
-    <row r="408" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="408" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A408" t="s">
         <v>18</v>
       </c>
@@ -29359,7 +29380,7 @@
         <v>1700</v>
       </c>
     </row>
-    <row r="410" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="410" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A410" t="s">
         <v>18</v>
       </c>
@@ -29403,7 +29424,7 @@
         <v>1704</v>
       </c>
     </row>
-    <row r="411" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="411" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A411" t="s">
         <v>18</v>
       </c>
@@ -29447,7 +29468,7 @@
         <v>1709</v>
       </c>
     </row>
-    <row r="412" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="412" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A412" t="s">
         <v>1710</v>
       </c>
@@ -29482,7 +29503,7 @@
         <v>1716</v>
       </c>
     </row>
-    <row r="413" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="413" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A413" t="s">
         <v>1710</v>
       </c>
@@ -29514,7 +29535,7 @@
         <v>1718</v>
       </c>
     </row>
-    <row r="414" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="414" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A414" t="s">
         <v>1710</v>
       </c>
@@ -29546,7 +29567,7 @@
         <v>1720</v>
       </c>
     </row>
-    <row r="415" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="415" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A415" t="s">
         <v>1710</v>
       </c>
@@ -29575,7 +29596,7 @@
         <v>1724</v>
       </c>
     </row>
-    <row r="416" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="416" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A416" t="s">
         <v>1710</v>
       </c>
@@ -29604,7 +29625,7 @@
         <v>1724</v>
       </c>
     </row>
-    <row r="417" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="417" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A417" t="s">
         <v>1710</v>
       </c>
@@ -29633,7 +29654,7 @@
         <v>1724</v>
       </c>
     </row>
-    <row r="418" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="418" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A418" t="s">
         <v>1710</v>
       </c>
@@ -29662,7 +29683,7 @@
         <v>1724</v>
       </c>
     </row>
-    <row r="419" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="419" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A419" t="s">
         <v>1710</v>
       </c>
@@ -29691,7 +29712,7 @@
         <v>1724</v>
       </c>
     </row>
-    <row r="420" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="420" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A420" t="s">
         <v>1710</v>
       </c>
@@ -29723,7 +29744,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="421" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="421" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A421" t="s">
         <v>1710</v>
       </c>
@@ -29755,7 +29776,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="422" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="422" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A422" t="s">
         <v>1710</v>
       </c>
@@ -29787,7 +29808,7 @@
         <v>1729</v>
       </c>
     </row>
-    <row r="423" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="423" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A423" t="s">
         <v>1710</v>
       </c>
@@ -29819,7 +29840,7 @@
         <v>1736</v>
       </c>
     </row>
-    <row r="424" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="424" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A424" t="s">
         <v>1710</v>
       </c>
@@ -29851,7 +29872,7 @@
         <v>1736</v>
       </c>
     </row>
-    <row r="425" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="425" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A425" t="s">
         <v>1710</v>
       </c>
@@ -29883,7 +29904,7 @@
         <v>1736</v>
       </c>
     </row>
-    <row r="426" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="426" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A426" t="s">
         <v>1710</v>
       </c>
@@ -29915,7 +29936,7 @@
         <v>1736</v>
       </c>
     </row>
-    <row r="427" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="427" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A427" t="s">
         <v>1710</v>
       </c>
@@ -29947,7 +29968,7 @@
         <v>1736</v>
       </c>
     </row>
-    <row r="428" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="428" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A428" t="s">
         <v>1710</v>
       </c>
@@ -29979,7 +30000,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="429" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="429" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A429" t="s">
         <v>1710</v>
       </c>
@@ -30011,7 +30032,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="430" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="430" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A430" t="s">
         <v>1710</v>
       </c>
@@ -30043,7 +30064,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="431" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="431" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A431" t="s">
         <v>1710</v>
       </c>
@@ -30075,7 +30096,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="432" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="432" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A432" t="s">
         <v>1710</v>
       </c>
@@ -30107,7 +30128,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="433" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="433" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A433" t="s">
         <v>1710</v>
       </c>
@@ -30139,7 +30160,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="434" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="434" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A434" t="s">
         <v>1710</v>
       </c>
@@ -30171,7 +30192,7 @@
         <v>1742</v>
       </c>
     </row>
-    <row r="435" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="435" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A435" t="s">
         <v>1710</v>
       </c>
@@ -30203,7 +30224,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="436" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="436" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A436" t="s">
         <v>1710</v>
       </c>
@@ -30235,7 +30256,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="437" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="437" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A437" t="s">
         <v>1710</v>
       </c>
@@ -30267,7 +30288,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="438" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="438" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A438" t="s">
         <v>1710</v>
       </c>
@@ -30299,7 +30320,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="439" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="439" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A439" t="s">
         <v>1710</v>
       </c>
@@ -30331,7 +30352,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="440" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="440" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A440" t="s">
         <v>1710</v>
       </c>
@@ -30363,7 +30384,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="441" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="441" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A441" t="s">
         <v>1710</v>
       </c>
@@ -30395,7 +30416,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="442" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="442" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A442" t="s">
         <v>1710</v>
       </c>
@@ -30427,7 +30448,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="443" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="443" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A443" t="s">
         <v>1710</v>
       </c>
@@ -30459,7 +30480,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="444" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="444" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A444" t="s">
         <v>1710</v>
       </c>
@@ -30491,7 +30512,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="445" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="445" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A445" t="s">
         <v>1710</v>
       </c>
@@ -30523,7 +30544,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="446" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="446" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A446" t="s">
         <v>1710</v>
       </c>
@@ -30555,7 +30576,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="447" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="447" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A447" t="s">
         <v>1710</v>
       </c>
@@ -30587,7 +30608,7 @@
         <v>1749</v>
       </c>
     </row>
-    <row r="448" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="448" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A448" t="s">
         <v>1710</v>
       </c>
@@ -30619,7 +30640,7 @@
         <v>1754</v>
       </c>
     </row>
-    <row r="449" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="449" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A449" t="s">
         <v>1710</v>
       </c>
@@ -30651,7 +30672,7 @@
         <v>1754</v>
       </c>
     </row>
-    <row r="450" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="450" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A450" t="s">
         <v>1710</v>
       </c>
@@ -30683,7 +30704,7 @@
         <v>1754</v>
       </c>
     </row>
-    <row r="451" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="451" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A451" t="s">
         <v>1710</v>
       </c>
@@ -30715,7 +30736,7 @@
         <v>1757</v>
       </c>
     </row>
-    <row r="452" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="452" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A452" t="s">
         <v>1710</v>
       </c>
@@ -30747,7 +30768,7 @@
         <v>1757</v>
       </c>
     </row>
-    <row r="453" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="453" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A453" t="s">
         <v>1758</v>
       </c>
@@ -30791,7 +30812,7 @@
         <v>1764</v>
       </c>
     </row>
-    <row r="454" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="454" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A454" t="s">
         <v>1758</v>
       </c>
@@ -30835,7 +30856,7 @@
         <v>1768</v>
       </c>
     </row>
-    <row r="455" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="455" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A455" t="s">
         <v>1758</v>
       </c>
@@ -30876,7 +30897,7 @@
         <v>1772</v>
       </c>
     </row>
-    <row r="456" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="456" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A456" t="s">
         <v>1758</v>
       </c>
@@ -30917,7 +30938,7 @@
         <v>1776</v>
       </c>
     </row>
-    <row r="457" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="457" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A457" t="s">
         <v>1758</v>
       </c>
@@ -30999,7 +31020,7 @@
         <v>1785</v>
       </c>
     </row>
-    <row r="459" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="459" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A459" t="s">
         <v>1758</v>
       </c>
@@ -31043,7 +31064,7 @@
         <v>1790</v>
       </c>
     </row>
-    <row r="460" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="460" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A460" t="s">
         <v>1758</v>
       </c>
@@ -31084,7 +31105,7 @@
         <v>1794</v>
       </c>
     </row>
-    <row r="461" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="461" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A461" t="s">
         <v>1758</v>
       </c>
@@ -31128,7 +31149,7 @@
         <v>1799</v>
       </c>
     </row>
-    <row r="462" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="462" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A462" t="s">
         <v>1758</v>
       </c>
@@ -31169,7 +31190,7 @@
         <v>1803</v>
       </c>
     </row>
-    <row r="463" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="463" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A463" t="s">
         <v>1758</v>
       </c>
@@ -31213,7 +31234,7 @@
         <v>1807</v>
       </c>
     </row>
-    <row r="464" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="464" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A464" t="s">
         <v>1758</v>
       </c>
@@ -31254,7 +31275,7 @@
         <v>1811</v>
       </c>
     </row>
-    <row r="465" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="465" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A465" t="s">
         <v>1758</v>
       </c>
@@ -31298,7 +31319,7 @@
         <v>1816</v>
       </c>
     </row>
-    <row r="466" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="466" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A466" t="s">
         <v>1758</v>
       </c>
@@ -31339,7 +31360,7 @@
         <v>1821</v>
       </c>
     </row>
-    <row r="467" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="467" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A467" t="s">
         <v>1758</v>
       </c>
@@ -31383,7 +31404,7 @@
         <v>1828</v>
       </c>
     </row>
-    <row r="468" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="468" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A468" t="s">
         <v>1758</v>
       </c>
@@ -31512,7 +31533,7 @@
         <v>1841</v>
       </c>
     </row>
-    <row r="471" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="471" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A471" t="s">
         <v>1758</v>
       </c>
@@ -31556,7 +31577,7 @@
         <v>1845</v>
       </c>
     </row>
-    <row r="472" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="472" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A472" t="s">
         <v>1758</v>
       </c>
@@ -31597,7 +31618,7 @@
         <v>1848</v>
       </c>
     </row>
-    <row r="473" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="473" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A473" t="s">
         <v>1758</v>
       </c>
@@ -31638,7 +31659,7 @@
         <v>1852</v>
       </c>
     </row>
-    <row r="474" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="474" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A474" t="s">
         <v>1758</v>
       </c>
@@ -31679,7 +31700,7 @@
         <v>1857</v>
       </c>
     </row>
-    <row r="475" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="475" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A475" t="s">
         <v>1758</v>
       </c>
@@ -31723,7 +31744,7 @@
         <v>1863</v>
       </c>
     </row>
-    <row r="476" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="476" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A476" t="s">
         <v>1758</v>
       </c>
@@ -31767,7 +31788,7 @@
         <v>1869</v>
       </c>
     </row>
-    <row r="477" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="477" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A477" t="s">
         <v>1758</v>
       </c>
@@ -31808,7 +31829,7 @@
         <v>1873</v>
       </c>
     </row>
-    <row r="478" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="478" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A478" t="s">
         <v>1758</v>
       </c>
@@ -31849,7 +31870,7 @@
         <v>1878</v>
       </c>
     </row>
-    <row r="479" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="479" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A479" t="s">
         <v>1758</v>
       </c>
@@ -31890,7 +31911,7 @@
         <v>1882</v>
       </c>
     </row>
-    <row r="480" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="480" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A480" t="s">
         <v>1758</v>
       </c>
@@ -31972,7 +31993,7 @@
         <v>1891</v>
       </c>
     </row>
-    <row r="482" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="482" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A482" t="s">
         <v>1758</v>
       </c>
@@ -32013,7 +32034,7 @@
         <v>1897</v>
       </c>
     </row>
-    <row r="483" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="483" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A483" t="s">
         <v>1758</v>
       </c>
@@ -32098,7 +32119,7 @@
         <v>1907</v>
       </c>
     </row>
-    <row r="485" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="485" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A485" t="s">
         <v>1758</v>
       </c>
@@ -32142,7 +32163,7 @@
         <v>1911</v>
       </c>
     </row>
-    <row r="486" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="486" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A486" t="s">
         <v>1758</v>
       </c>
@@ -32186,7 +32207,7 @@
         <v>1915</v>
       </c>
     </row>
-    <row r="487" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="487" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A487" t="s">
         <v>1758</v>
       </c>
@@ -32230,7 +32251,7 @@
         <v>1919</v>
       </c>
     </row>
-    <row r="488" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="488" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A488" t="s">
         <v>1758</v>
       </c>
@@ -32271,7 +32292,7 @@
         <v>1923</v>
       </c>
     </row>
-    <row r="489" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="489" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A489" t="s">
         <v>1758</v>
       </c>
@@ -32312,7 +32333,7 @@
         <v>1926</v>
       </c>
     </row>
-    <row r="490" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="490" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A490" t="s">
         <v>1758</v>
       </c>
@@ -32353,7 +32374,7 @@
         <v>1931</v>
       </c>
     </row>
-    <row r="491" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="491" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A491" t="s">
         <v>1758</v>
       </c>
@@ -32397,7 +32418,7 @@
         <v>1935</v>
       </c>
     </row>
-    <row r="492" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="492" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A492" t="s">
         <v>1758</v>
       </c>
@@ -32438,7 +32459,7 @@
         <v>1939</v>
       </c>
     </row>
-    <row r="493" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="493" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A493" t="s">
         <v>1758</v>
       </c>
@@ -32479,7 +32500,7 @@
         <v>1943</v>
       </c>
     </row>
-    <row r="494" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="494" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A494" t="s">
         <v>1758</v>
       </c>
@@ -32567,7 +32588,7 @@
         <v>1951</v>
       </c>
     </row>
-    <row r="496" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="496" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A496" t="s">
         <v>1758</v>
       </c>
@@ -32611,7 +32632,7 @@
         <v>1955</v>
       </c>
     </row>
-    <row r="497" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="497" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A497" t="s">
         <v>1758</v>
       </c>
@@ -32655,7 +32676,7 @@
         <v>1960</v>
       </c>
     </row>
-    <row r="498" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="498" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A498" t="s">
         <v>1758</v>
       </c>
@@ -32696,7 +32717,7 @@
         <v>1965</v>
       </c>
     </row>
-    <row r="499" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="499" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A499" t="s">
         <v>1758</v>
       </c>
@@ -32737,7 +32758,7 @@
         <v>1970</v>
       </c>
     </row>
-    <row r="500" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="500" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A500" t="s">
         <v>1758</v>
       </c>
@@ -32778,7 +32799,7 @@
         <v>1974</v>
       </c>
     </row>
-    <row r="501" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="501" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A501" t="s">
         <v>1758</v>
       </c>
@@ -32822,7 +32843,7 @@
         <v>1978</v>
       </c>
     </row>
-    <row r="502" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="502" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A502" t="s">
         <v>1758</v>
       </c>
@@ -32863,7 +32884,7 @@
         <v>1984</v>
       </c>
     </row>
-    <row r="503" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="503" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A503" t="s">
         <v>1758</v>
       </c>
@@ -32904,7 +32925,7 @@
         <v>1988</v>
       </c>
     </row>
-    <row r="504" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="504" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A504" t="s">
         <v>1758</v>
       </c>
@@ -32945,7 +32966,7 @@
         <v>1992</v>
       </c>
     </row>
-    <row r="505" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="505" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A505" t="s">
         <v>1758</v>
       </c>
@@ -32986,7 +33007,7 @@
         <v>1995</v>
       </c>
     </row>
-    <row r="506" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="506" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A506" t="s">
         <v>1758</v>
       </c>
@@ -33027,7 +33048,7 @@
         <v>1999</v>
       </c>
     </row>
-    <row r="507" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="507" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A507" t="s">
         <v>1758</v>
       </c>
@@ -33068,7 +33089,7 @@
         <v>2004</v>
       </c>
     </row>
-    <row r="508" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="508" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A508" t="s">
         <v>1758</v>
       </c>
@@ -33112,7 +33133,7 @@
         <v>2007</v>
       </c>
     </row>
-    <row r="509" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="509" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A509" t="s">
         <v>1758</v>
       </c>
@@ -33153,7 +33174,7 @@
         <v>2012</v>
       </c>
     </row>
-    <row r="510" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="510" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A510" t="s">
         <v>1758</v>
       </c>
@@ -33194,7 +33215,7 @@
         <v>2016</v>
       </c>
     </row>
-    <row r="511" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="511" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A511" t="s">
         <v>1758</v>
       </c>
@@ -33235,7 +33256,7 @@
         <v>2020</v>
       </c>
     </row>
-    <row r="512" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="512" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A512" t="s">
         <v>1758</v>
       </c>
@@ -33276,7 +33297,7 @@
         <v>2025</v>
       </c>
     </row>
-    <row r="513" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="513" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A513" t="s">
         <v>1758</v>
       </c>
@@ -33320,7 +33341,7 @@
         <v>2029</v>
       </c>
     </row>
-    <row r="514" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="514" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A514" t="s">
         <v>1758</v>
       </c>
@@ -33364,7 +33385,7 @@
         <v>2034</v>
       </c>
     </row>
-    <row r="515" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="515" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A515" t="s">
         <v>1758</v>
       </c>
@@ -33405,7 +33426,7 @@
         <v>2039</v>
       </c>
     </row>
-    <row r="516" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="516" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A516" t="s">
         <v>1758</v>
       </c>
@@ -33490,7 +33511,7 @@
         <v>2049</v>
       </c>
     </row>
-    <row r="518" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="518" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A518" t="s">
         <v>1758</v>
       </c>
@@ -33531,7 +33552,7 @@
         <v>2053</v>
       </c>
     </row>
-    <row r="519" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="519" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A519" t="s">
         <v>1758</v>
       </c>
@@ -33563,7 +33584,7 @@
         <v>2059</v>
       </c>
     </row>
-    <row r="520" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="520" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A520" t="s">
         <v>1758</v>
       </c>
@@ -33604,7 +33625,7 @@
         <v>2063</v>
       </c>
     </row>
-    <row r="521" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="521" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A521" t="s">
         <v>1758</v>
       </c>
@@ -33645,7 +33666,7 @@
         <v>2067</v>
       </c>
     </row>
-    <row r="522" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="522" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A522" t="s">
         <v>1758</v>
       </c>
@@ -33686,7 +33707,7 @@
         <v>2071</v>
       </c>
     </row>
-    <row r="523" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="523" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A523" t="s">
         <v>1758</v>
       </c>
@@ -33727,7 +33748,7 @@
         <v>2075</v>
       </c>
     </row>
-    <row r="524" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="524" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A524" t="s">
         <v>1758</v>
       </c>
@@ -33771,7 +33792,7 @@
         <v>2080</v>
       </c>
     </row>
-    <row r="525" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="525" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A525" t="s">
         <v>1758</v>
       </c>
@@ -33812,7 +33833,7 @@
         <v>2084</v>
       </c>
     </row>
-    <row r="526" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="526" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A526" t="s">
         <v>1758</v>
       </c>
@@ -33853,7 +33874,7 @@
         <v>2089</v>
       </c>
     </row>
-    <row r="527" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="527" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A527" t="s">
         <v>1758</v>
       </c>
@@ -33938,7 +33959,7 @@
         <v>2099</v>
       </c>
     </row>
-    <row r="529" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="529" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A529" t="s">
         <v>1758</v>
       </c>
@@ -33979,7 +34000,7 @@
         <v>2104</v>
       </c>
     </row>
-    <row r="530" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="530" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A530" t="s">
         <v>1758</v>
       </c>
@@ -34020,7 +34041,7 @@
         <v>2108</v>
       </c>
     </row>
-    <row r="531" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="531" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A531" t="s">
         <v>1758</v>
       </c>
@@ -34061,7 +34082,7 @@
         <v>2112</v>
       </c>
     </row>
-    <row r="532" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="532" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A532" t="s">
         <v>1758</v>
       </c>
@@ -34105,7 +34126,7 @@
         <v>2116</v>
       </c>
     </row>
-    <row r="533" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="533" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A533" t="s">
         <v>1758</v>
       </c>
@@ -34149,7 +34170,7 @@
         <v>2120</v>
       </c>
     </row>
-    <row r="534" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="534" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A534" t="s">
         <v>1758</v>
       </c>
@@ -34190,7 +34211,7 @@
         <v>2124</v>
       </c>
     </row>
-    <row r="535" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="535" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A535" t="s">
         <v>1758</v>
       </c>
@@ -34231,7 +34252,7 @@
         <v>2129</v>
       </c>
     </row>
-    <row r="536" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="536" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A536" t="s">
         <v>1758</v>
       </c>
@@ -34272,7 +34293,7 @@
         <v>2134</v>
       </c>
     </row>
-    <row r="537" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="537" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A537" t="s">
         <v>1758</v>
       </c>
@@ -34313,7 +34334,7 @@
         <v>2139</v>
       </c>
     </row>
-    <row r="538" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="538" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A538" t="s">
         <v>1758</v>
       </c>
@@ -34354,7 +34375,7 @@
         <v>2144</v>
       </c>
     </row>
-    <row r="539" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="539" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A539" t="s">
         <v>1758</v>
       </c>
@@ -34395,7 +34416,7 @@
         <v>2147</v>
       </c>
     </row>
-    <row r="540" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="540" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A540" t="s">
         <v>1758</v>
       </c>
@@ -34436,7 +34457,7 @@
         <v>2151</v>
       </c>
     </row>
-    <row r="541" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="541" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A541" t="s">
         <v>1758</v>
       </c>
@@ -34480,7 +34501,7 @@
         <v>2156</v>
       </c>
     </row>
-    <row r="542" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="542" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A542" t="s">
         <v>1758</v>
       </c>
@@ -34524,7 +34545,7 @@
         <v>2160</v>
       </c>
     </row>
-    <row r="543" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="543" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A543" t="s">
         <v>1758</v>
       </c>
@@ -34565,7 +34586,7 @@
         <v>2164</v>
       </c>
     </row>
-    <row r="544" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="544" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A544" t="s">
         <v>1758</v>
       </c>
@@ -34609,7 +34630,7 @@
         <v>2169</v>
       </c>
     </row>
-    <row r="545" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="545" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A545" t="s">
         <v>1758</v>
       </c>
@@ -34653,7 +34674,7 @@
         <v>2175</v>
       </c>
     </row>
-    <row r="546" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="546" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A546" t="s">
         <v>1758</v>
       </c>
@@ -34697,7 +34718,7 @@
         <v>2179</v>
       </c>
     </row>
-    <row r="547" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="547" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A547" t="s">
         <v>1758</v>
       </c>
@@ -34741,7 +34762,7 @@
         <v>2185</v>
       </c>
     </row>
-    <row r="548" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="548" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A548" t="s">
         <v>1758</v>
       </c>
@@ -34785,7 +34806,7 @@
         <v>2189</v>
       </c>
     </row>
-    <row r="549" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="549" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A549" t="s">
         <v>1758</v>
       </c>
@@ -34829,7 +34850,7 @@
         <v>2193</v>
       </c>
     </row>
-    <row r="550" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="550" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A550" t="s">
         <v>1758</v>
       </c>
@@ -34873,7 +34894,7 @@
         <v>2198</v>
       </c>
     </row>
-    <row r="551" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="551" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A551" t="s">
         <v>1758</v>
       </c>
@@ -34917,7 +34938,7 @@
         <v>2201</v>
       </c>
     </row>
-    <row r="552" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="552" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A552" t="s">
         <v>1758</v>
       </c>
@@ -34961,7 +34982,7 @@
         <v>2206</v>
       </c>
     </row>
-    <row r="553" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="553" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A553" t="s">
         <v>1758</v>
       </c>
@@ -35046,7 +35067,7 @@
         <v>2216</v>
       </c>
     </row>
-    <row r="555" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="555" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A555" t="s">
         <v>1758</v>
       </c>
@@ -35090,7 +35111,7 @@
         <v>2219</v>
       </c>
     </row>
-    <row r="556" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="556" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A556" t="s">
         <v>1758</v>
       </c>
@@ -35134,7 +35155,7 @@
         <v>2222</v>
       </c>
     </row>
-    <row r="557" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="557" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A557" t="s">
         <v>1758</v>
       </c>
@@ -35175,7 +35196,7 @@
         <v>2226</v>
       </c>
     </row>
-    <row r="558" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="558" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A558" t="s">
         <v>1758</v>
       </c>
@@ -35219,7 +35240,7 @@
         <v>2230</v>
       </c>
     </row>
-    <row r="559" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="559" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A559" t="s">
         <v>1758</v>
       </c>
@@ -35260,7 +35281,7 @@
         <v>2234</v>
       </c>
     </row>
-    <row r="560" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="560" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A560" t="s">
         <v>1758</v>
       </c>
@@ -35304,7 +35325,7 @@
         <v>2238</v>
       </c>
     </row>
-    <row r="561" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="561" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A561" t="s">
         <v>1758</v>
       </c>
@@ -35345,7 +35366,7 @@
         <v>2242</v>
       </c>
     </row>
-    <row r="562" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="562" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A562" t="s">
         <v>1758</v>
       </c>
@@ -35389,7 +35410,7 @@
         <v>2247</v>
       </c>
     </row>
-    <row r="563" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="563" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A563" t="s">
         <v>1758</v>
       </c>
@@ -35433,7 +35454,7 @@
         <v>2250</v>
       </c>
     </row>
-    <row r="564" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="564" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A564" t="s">
         <v>1758</v>
       </c>
@@ -35477,7 +35498,7 @@
         <v>2254</v>
       </c>
     </row>
-    <row r="565" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="565" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A565" t="s">
         <v>1758</v>
       </c>
@@ -35521,7 +35542,7 @@
         <v>2259</v>
       </c>
     </row>
-    <row r="566" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="566" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A566" t="s">
         <v>1758</v>
       </c>
@@ -35565,7 +35586,7 @@
         <v>2263</v>
       </c>
     </row>
-    <row r="567" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="567" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A567" t="s">
         <v>1758</v>
       </c>
@@ -35609,7 +35630,7 @@
         <v>2268</v>
       </c>
     </row>
-    <row r="568" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="568" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A568" t="s">
         <v>1758</v>
       </c>
@@ -35650,7 +35671,7 @@
         <v>2271</v>
       </c>
     </row>
-    <row r="569" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="569" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A569" t="s">
         <v>1758</v>
       </c>
@@ -35694,7 +35715,7 @@
         <v>2275</v>
       </c>
     </row>
-    <row r="570" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="570" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A570" t="s">
         <v>1758</v>
       </c>
@@ -35735,7 +35756,7 @@
         <v>2280</v>
       </c>
     </row>
-    <row r="571" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="571" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A571" t="s">
         <v>1758</v>
       </c>
@@ -35776,7 +35797,7 @@
         <v>2284</v>
       </c>
     </row>
-    <row r="572" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="572" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A572" t="s">
         <v>1758</v>
       </c>
@@ -35817,7 +35838,7 @@
         <v>2288</v>
       </c>
     </row>
-    <row r="573" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="573" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A573" t="s">
         <v>1758</v>
       </c>
@@ -35858,7 +35879,7 @@
         <v>2292</v>
       </c>
     </row>
-    <row r="574" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="574" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A574" t="s">
         <v>1758</v>
       </c>
@@ -35899,7 +35920,7 @@
         <v>2297</v>
       </c>
     </row>
-    <row r="575" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="575" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A575" t="s">
         <v>1758</v>
       </c>
@@ -35940,7 +35961,7 @@
         <v>2301</v>
       </c>
     </row>
-    <row r="576" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="576" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A576" t="s">
         <v>1758</v>
       </c>
@@ -35981,7 +36002,7 @@
         <v>2306</v>
       </c>
     </row>
-    <row r="577" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="577" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A577" t="s">
         <v>1758</v>
       </c>
@@ -36069,7 +36090,7 @@
         <v>2316</v>
       </c>
     </row>
-    <row r="579" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="579" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A579" t="s">
         <v>1758</v>
       </c>
@@ -36110,7 +36131,7 @@
         <v>2320</v>
       </c>
     </row>
-    <row r="580" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="580" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A580" t="s">
         <v>1758</v>
       </c>
@@ -36151,7 +36172,7 @@
         <v>2325</v>
       </c>
     </row>
-    <row r="581" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="581" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A581" t="s">
         <v>1758</v>
       </c>
@@ -36192,7 +36213,7 @@
         <v>2329</v>
       </c>
     </row>
-    <row r="582" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="582" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A582" t="s">
         <v>1758</v>
       </c>
@@ -36233,7 +36254,7 @@
         <v>2334</v>
       </c>
     </row>
-    <row r="583" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="583" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A583" t="s">
         <v>1758</v>
       </c>
@@ -36274,7 +36295,7 @@
         <v>2338</v>
       </c>
     </row>
-    <row r="584" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="584" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A584" t="s">
         <v>1758</v>
       </c>
@@ -36315,7 +36336,7 @@
         <v>2343</v>
       </c>
     </row>
-    <row r="585" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="585" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A585" t="s">
         <v>1758</v>
       </c>
@@ -36356,7 +36377,7 @@
         <v>2348</v>
       </c>
     </row>
-    <row r="586" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="586" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A586" t="s">
         <v>1758</v>
       </c>
@@ -36397,7 +36418,7 @@
         <v>2352</v>
       </c>
     </row>
-    <row r="587" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="587" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A587" t="s">
         <v>1758</v>
       </c>
@@ -36438,7 +36459,7 @@
         <v>2356</v>
       </c>
     </row>
-    <row r="588" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="588" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A588" t="s">
         <v>1758</v>
       </c>
@@ -36482,7 +36503,7 @@
         <v>2361</v>
       </c>
     </row>
-    <row r="589" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="589" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A589" t="s">
         <v>1758</v>
       </c>
@@ -36652,7 +36673,7 @@
         <v>2379</v>
       </c>
     </row>
-    <row r="593" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="593" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A593" t="s">
         <v>1758</v>
       </c>
@@ -36693,7 +36714,7 @@
         <v>2384</v>
       </c>
     </row>
-    <row r="594" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="594" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A594" t="s">
         <v>1758</v>
       </c>
@@ -36737,7 +36758,7 @@
         <v>2389</v>
       </c>
     </row>
-    <row r="595" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="595" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A595" t="s">
         <v>1758</v>
       </c>
@@ -36822,7 +36843,7 @@
         <v>2399</v>
       </c>
     </row>
-    <row r="597" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="597" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A597" t="s">
         <v>1758</v>
       </c>
@@ -36866,7 +36887,7 @@
         <v>2402</v>
       </c>
     </row>
-    <row r="598" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="598" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A598" t="s">
         <v>1758</v>
       </c>
@@ -36910,7 +36931,7 @@
         <v>2407</v>
       </c>
     </row>
-    <row r="599" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="599" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A599" t="s">
         <v>1758</v>
       </c>
@@ -36954,7 +36975,7 @@
         <v>2411</v>
       </c>
     </row>
-    <row r="600" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="600" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A600" t="s">
         <v>1758</v>
       </c>
@@ -36995,7 +37016,7 @@
         <v>2415</v>
       </c>
     </row>
-    <row r="601" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="601" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A601" t="s">
         <v>1758</v>
       </c>
@@ -37080,7 +37101,7 @@
         <v>2423</v>
       </c>
     </row>
-    <row r="603" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="603" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A603" t="s">
         <v>1758</v>
       </c>
@@ -37124,7 +37145,7 @@
         <v>2427</v>
       </c>
     </row>
-    <row r="604" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="604" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A604" t="s">
         <v>1758</v>
       </c>
@@ -37168,7 +37189,7 @@
         <v>2430</v>
       </c>
     </row>
-    <row r="605" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="605" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A605" t="s">
         <v>1758</v>
       </c>
@@ -37212,7 +37233,7 @@
         <v>2435</v>
       </c>
     </row>
-    <row r="606" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="606" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A606" t="s">
         <v>1758</v>
       </c>
@@ -37256,7 +37277,7 @@
         <v>2440</v>
       </c>
     </row>
-    <row r="607" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="607" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A607" t="s">
         <v>1758</v>
       </c>
@@ -37297,7 +37318,7 @@
         <v>2445</v>
       </c>
     </row>
-    <row r="608" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="608" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A608" t="s">
         <v>1758</v>
       </c>
@@ -37341,7 +37362,7 @@
         <v>2449</v>
       </c>
     </row>
-    <row r="609" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="609" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A609" t="s">
         <v>1758</v>
       </c>
@@ -37382,7 +37403,7 @@
         <v>2453</v>
       </c>
     </row>
-    <row r="610" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="610" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A610" t="s">
         <v>1758</v>
       </c>
@@ -37423,7 +37444,7 @@
         <v>2457</v>
       </c>
     </row>
-    <row r="611" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="611" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A611" t="s">
         <v>1758</v>
       </c>
@@ -37464,7 +37485,7 @@
         <v>2461</v>
       </c>
     </row>
-    <row r="612" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="612" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A612" t="s">
         <v>1758</v>
       </c>
@@ -37505,7 +37526,7 @@
         <v>2466</v>
       </c>
     </row>
-    <row r="613" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="613" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A613" t="s">
         <v>1758</v>
       </c>
@@ -37546,7 +37567,7 @@
         <v>2470</v>
       </c>
     </row>
-    <row r="614" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="614" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A614" t="s">
         <v>1758</v>
       </c>
@@ -37587,7 +37608,7 @@
         <v>2474</v>
       </c>
     </row>
-    <row r="615" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="615" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A615" t="s">
         <v>1758</v>
       </c>
@@ -37622,7 +37643,7 @@
         <v>2479</v>
       </c>
     </row>
-    <row r="616" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="616" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A616" t="s">
         <v>1758</v>
       </c>
@@ -37663,7 +37684,7 @@
         <v>2484</v>
       </c>
     </row>
-    <row r="617" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="617" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A617" t="s">
         <v>1758</v>
       </c>
@@ -37707,7 +37728,7 @@
         <v>2489</v>
       </c>
     </row>
-    <row r="618" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="618" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A618" t="s">
         <v>1758</v>
       </c>
@@ -37789,7 +37810,7 @@
         <v>2497</v>
       </c>
     </row>
-    <row r="620" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="620" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A620" t="s">
         <v>1758</v>
       </c>
@@ -37833,7 +37854,7 @@
         <v>2501</v>
       </c>
     </row>
-    <row r="621" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="621" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A621" t="s">
         <v>1758</v>
       </c>
@@ -37877,7 +37898,7 @@
         <v>2505</v>
       </c>
     </row>
-    <row r="622" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="622" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A622" t="s">
         <v>1758</v>
       </c>
@@ -37921,7 +37942,7 @@
         <v>2510</v>
       </c>
     </row>
-    <row r="623" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="623" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A623" t="s">
         <v>1758</v>
       </c>
@@ -37965,7 +37986,7 @@
         <v>2516</v>
       </c>
     </row>
-    <row r="624" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="624" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A624" t="s">
         <v>1758</v>
       </c>
@@ -38009,7 +38030,7 @@
         <v>2520</v>
       </c>
     </row>
-    <row r="625" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="625" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A625" t="s">
         <v>1758</v>
       </c>
@@ -38053,7 +38074,7 @@
         <v>2525</v>
       </c>
     </row>
-    <row r="626" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="626" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A626" t="s">
         <v>1758</v>
       </c>
@@ -38094,7 +38115,7 @@
         <v>2527</v>
       </c>
     </row>
-    <row r="627" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="627" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A627" t="s">
         <v>1758</v>
       </c>
@@ -38135,7 +38156,7 @@
         <v>2532</v>
       </c>
     </row>
-    <row r="628" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="628" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A628" t="s">
         <v>1758</v>
       </c>
@@ -38179,7 +38200,7 @@
         <v>2537</v>
       </c>
     </row>
-    <row r="629" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="629" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A629" t="s">
         <v>1758</v>
       </c>
@@ -38223,7 +38244,7 @@
         <v>2542</v>
       </c>
     </row>
-    <row r="630" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="630" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A630" t="s">
         <v>1758</v>
       </c>
@@ -38267,7 +38288,7 @@
         <v>2547</v>
       </c>
     </row>
-    <row r="631" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="631" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A631" t="s">
         <v>1758</v>
       </c>
@@ -38311,7 +38332,7 @@
         <v>2552</v>
       </c>
     </row>
-    <row r="632" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="632" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A632" t="s">
         <v>1758</v>
       </c>
@@ -38355,7 +38376,7 @@
         <v>2557</v>
       </c>
     </row>
-    <row r="633" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="633" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A633" t="s">
         <v>1758</v>
       </c>
@@ -38399,7 +38420,7 @@
         <v>2562</v>
       </c>
     </row>
-    <row r="634" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="634" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A634" t="s">
         <v>1758</v>
       </c>
@@ -38440,7 +38461,7 @@
         <v>2566</v>
       </c>
     </row>
-    <row r="635" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="635" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A635" t="s">
         <v>1758</v>
       </c>
@@ -38484,7 +38505,7 @@
         <v>2571</v>
       </c>
     </row>
-    <row r="636" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="636" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A636" t="s">
         <v>1758</v>
       </c>
@@ -38528,7 +38549,7 @@
         <v>2575</v>
       </c>
     </row>
-    <row r="637" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="637" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A637" t="s">
         <v>1758</v>
       </c>
@@ -38563,7 +38584,7 @@
         <v>2579</v>
       </c>
     </row>
-    <row r="638" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="638" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A638" t="s">
         <v>1758</v>
       </c>
@@ -38604,7 +38625,7 @@
         <v>2584</v>
       </c>
     </row>
-    <row r="639" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="639" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A639" t="s">
         <v>1758</v>
       </c>
@@ -38645,7 +38666,7 @@
         <v>2590</v>
       </c>
     </row>
-    <row r="640" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="640" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A640" t="s">
         <v>1758</v>
       </c>
@@ -38686,7 +38707,7 @@
         <v>2594</v>
       </c>
     </row>
-    <row r="641" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="641" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A641" t="s">
         <v>1758</v>
       </c>
@@ -38727,7 +38748,7 @@
         <v>2599</v>
       </c>
     </row>
-    <row r="642" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="642" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A642" t="s">
         <v>1758</v>
       </c>
@@ -38768,7 +38789,7 @@
         <v>2604</v>
       </c>
     </row>
-    <row r="643" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="643" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A643" t="s">
         <v>1758</v>
       </c>
@@ -38812,7 +38833,7 @@
         <v>2610</v>
       </c>
     </row>
-    <row r="644" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="644" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A644" t="s">
         <v>1758</v>
       </c>
@@ -38853,7 +38874,7 @@
         <v>2615</v>
       </c>
     </row>
-    <row r="645" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="645" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A645" t="s">
         <v>1758</v>
       </c>
@@ -38894,7 +38915,7 @@
         <v>2620</v>
       </c>
     </row>
-    <row r="646" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="646" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A646" t="s">
         <v>1758</v>
       </c>
@@ -38938,7 +38959,7 @@
         <v>2624</v>
       </c>
     </row>
-    <row r="647" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="647" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A647" t="s">
         <v>1758</v>
       </c>
@@ -38982,7 +39003,7 @@
         <v>2628</v>
       </c>
     </row>
-    <row r="648" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="648" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A648" t="s">
         <v>1758</v>
       </c>
@@ -39023,7 +39044,7 @@
         <v>2634</v>
       </c>
     </row>
-    <row r="649" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="649" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A649" t="s">
         <v>1758</v>
       </c>
@@ -39067,7 +39088,7 @@
         <v>2638</v>
       </c>
     </row>
-    <row r="650" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="650" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A650" t="s">
         <v>1758</v>
       </c>
@@ -39111,7 +39132,7 @@
         <v>2642</v>
       </c>
     </row>
-    <row r="651" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="651" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A651" t="s">
         <v>1758</v>
       </c>
@@ -39155,7 +39176,7 @@
         <v>2647</v>
       </c>
     </row>
-    <row r="652" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="652" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A652" t="s">
         <v>1758</v>
       </c>
@@ -39196,7 +39217,7 @@
         <v>2650</v>
       </c>
     </row>
-    <row r="653" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="653" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A653" t="s">
         <v>1758</v>
       </c>
@@ -39240,7 +39261,7 @@
         <v>2655</v>
       </c>
     </row>
-    <row r="654" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="654" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A654" t="s">
         <v>1758</v>
       </c>
@@ -39284,7 +39305,7 @@
         <v>2660</v>
       </c>
     </row>
-    <row r="655" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="655" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A655" t="s">
         <v>1758</v>
       </c>
@@ -39328,7 +39349,7 @@
         <v>2665</v>
       </c>
     </row>
-    <row r="656" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="656" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A656" t="s">
         <v>1758</v>
       </c>
@@ -39372,7 +39393,7 @@
         <v>2669</v>
       </c>
     </row>
-    <row r="657" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="657" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A657" t="s">
         <v>1758</v>
       </c>
@@ -39416,7 +39437,7 @@
         <v>2674</v>
       </c>
     </row>
-    <row r="658" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="658" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A658" t="s">
         <v>1758</v>
       </c>
@@ -39460,7 +39481,7 @@
         <v>2678</v>
       </c>
     </row>
-    <row r="659" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="659" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A659" t="s">
         <v>1758</v>
       </c>
@@ -39501,7 +39522,7 @@
         <v>2683</v>
       </c>
     </row>
-    <row r="660" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="660" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A660" t="s">
         <v>1758</v>
       </c>
@@ -39533,7 +39554,7 @@
         <v>2689</v>
       </c>
     </row>
-    <row r="661" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="661" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A661" t="s">
         <v>1758</v>
       </c>
@@ -39577,7 +39598,7 @@
         <v>2693</v>
       </c>
     </row>
-    <row r="662" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="662" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A662" t="s">
         <v>1758</v>
       </c>
@@ -39618,7 +39639,7 @@
         <v>2698</v>
       </c>
     </row>
-    <row r="663" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="663" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A663" t="s">
         <v>1758</v>
       </c>
@@ -39659,7 +39680,7 @@
         <v>2704</v>
       </c>
     </row>
-    <row r="664" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="664" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A664" t="s">
         <v>1758</v>
       </c>
@@ -39703,7 +39724,7 @@
         <v>2708</v>
       </c>
     </row>
-    <row r="665" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="665" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A665" t="s">
         <v>1758</v>
       </c>
@@ -39832,7 +39853,7 @@
         <v>1837</v>
       </c>
     </row>
-    <row r="668" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="668" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A668" t="s">
         <v>1758</v>
       </c>
@@ -39873,7 +39894,7 @@
         <v>2722</v>
       </c>
     </row>
-    <row r="669" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="669" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A669" t="s">
         <v>1758</v>
       </c>
@@ -39914,7 +39935,7 @@
         <v>2728</v>
       </c>
     </row>
-    <row r="670" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="670" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A670" t="s">
         <v>1758</v>
       </c>
@@ -39958,7 +39979,7 @@
         <v>2733</v>
       </c>
     </row>
-    <row r="671" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="671" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A671" t="s">
         <v>1758</v>
       </c>
@@ -40002,7 +40023,7 @@
         <v>2737</v>
       </c>
     </row>
-    <row r="672" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="672" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A672" t="s">
         <v>1758</v>
       </c>
@@ -40046,7 +40067,7 @@
         <v>2742</v>
       </c>
     </row>
-    <row r="673" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="673" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A673" t="s">
         <v>1758</v>
       </c>
@@ -40090,7 +40111,7 @@
         <v>2747</v>
       </c>
     </row>
-    <row r="674" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="674" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A674" t="s">
         <v>1758</v>
       </c>
@@ -40131,7 +40152,7 @@
         <v>2752</v>
       </c>
     </row>
-    <row r="675" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="675" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A675" t="s">
         <v>1758</v>
       </c>
@@ -40175,7 +40196,7 @@
         <v>2757</v>
       </c>
     </row>
-    <row r="676" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="676" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A676" t="s">
         <v>1758</v>
       </c>
@@ -40219,7 +40240,7 @@
         <v>2763</v>
       </c>
     </row>
-    <row r="677" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="677" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A677" t="s">
         <v>1758</v>
       </c>
@@ -40263,7 +40284,7 @@
         <v>2767</v>
       </c>
     </row>
-    <row r="678" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="678" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A678" t="s">
         <v>1758</v>
       </c>
@@ -40307,7 +40328,7 @@
         <v>2772</v>
       </c>
     </row>
-    <row r="679" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="679" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A679" t="s">
         <v>1758</v>
       </c>
@@ -40351,7 +40372,7 @@
         <v>2774</v>
       </c>
     </row>
-    <row r="680" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="680" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A680" t="s">
         <v>1758</v>
       </c>
@@ -40392,7 +40413,7 @@
         <v>2779</v>
       </c>
     </row>
-    <row r="681" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="681" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A681" t="s">
         <v>1758</v>
       </c>
@@ -40433,7 +40454,7 @@
         <v>2784</v>
       </c>
     </row>
-    <row r="682" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="682" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A682" t="s">
         <v>1758</v>
       </c>
@@ -40477,7 +40498,7 @@
         <v>2789</v>
       </c>
     </row>
-    <row r="683" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="683" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A683" t="s">
         <v>1758</v>
       </c>
@@ -40521,7 +40542,7 @@
         <v>2794</v>
       </c>
     </row>
-    <row r="684" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="684" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A684" t="s">
         <v>1758</v>
       </c>
@@ -40562,7 +40583,7 @@
         <v>2800</v>
       </c>
     </row>
-    <row r="685" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="685" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A685" t="s">
         <v>1758</v>
       </c>
@@ -40603,7 +40624,7 @@
         <v>2804</v>
       </c>
     </row>
-    <row r="686" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="686" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A686" t="s">
         <v>1758</v>
       </c>
@@ -40647,7 +40668,7 @@
         <v>2809</v>
       </c>
     </row>
-    <row r="687" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="687" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A687" t="s">
         <v>1758</v>
       </c>
@@ -40691,7 +40712,7 @@
         <v>2814</v>
       </c>
     </row>
-    <row r="688" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="688" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A688" t="s">
         <v>1758</v>
       </c>
@@ -40735,7 +40756,7 @@
         <v>2819</v>
       </c>
     </row>
-    <row r="689" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="689" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A689" t="s">
         <v>1758</v>
       </c>
@@ -40776,7 +40797,7 @@
         <v>2823</v>
       </c>
     </row>
-    <row r="690" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="690" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A690" t="s">
         <v>1758</v>
       </c>
@@ -40820,7 +40841,7 @@
         <v>2828</v>
       </c>
     </row>
-    <row r="691" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="691" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A691" t="s">
         <v>1758</v>
       </c>
@@ -40861,7 +40882,7 @@
         <v>2832</v>
       </c>
     </row>
-    <row r="692" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="692" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A692" t="s">
         <v>1758</v>
       </c>
@@ -40905,7 +40926,7 @@
         <v>2836</v>
       </c>
     </row>
-    <row r="693" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="693" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A693" t="s">
         <v>1758</v>
       </c>
@@ -40990,7 +41011,7 @@
         <v>2846</v>
       </c>
     </row>
-    <row r="695" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="695" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A695" t="s">
         <v>1758</v>
       </c>
@@ -41031,7 +41052,7 @@
         <v>2851</v>
       </c>
     </row>
-    <row r="696" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="696" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A696" t="s">
         <v>1758</v>
       </c>
@@ -41075,7 +41096,7 @@
         <v>2854</v>
       </c>
     </row>
-    <row r="697" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="697" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A697" t="s">
         <v>1758</v>
       </c>
@@ -41116,7 +41137,7 @@
         <v>2858</v>
       </c>
     </row>
-    <row r="698" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="698" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A698" t="s">
         <v>1758</v>
       </c>
@@ -41157,7 +41178,7 @@
         <v>2863</v>
       </c>
     </row>
-    <row r="699" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="699" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A699" t="s">
         <v>1758</v>
       </c>
@@ -41201,7 +41222,7 @@
         <v>2868</v>
       </c>
     </row>
-    <row r="700" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="700" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A700" t="s">
         <v>1758</v>
       </c>
@@ -41245,7 +41266,7 @@
         <v>2873</v>
       </c>
     </row>
-    <row r="701" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="701" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A701" t="s">
         <v>1758</v>
       </c>
@@ -41289,7 +41310,7 @@
         <v>2878</v>
       </c>
     </row>
-    <row r="702" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="702" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A702" t="s">
         <v>1758</v>
       </c>
@@ -41330,7 +41351,7 @@
         <v>2882</v>
       </c>
     </row>
-    <row r="703" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="703" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A703" t="s">
         <v>1758</v>
       </c>
@@ -41374,7 +41395,7 @@
         <v>2887</v>
       </c>
     </row>
-    <row r="704" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="704" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A704" t="s">
         <v>1758</v>
       </c>
@@ -41415,7 +41436,7 @@
         <v>2892</v>
       </c>
     </row>
-    <row r="705" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="705" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A705" t="s">
         <v>1758</v>
       </c>
@@ -41459,7 +41480,7 @@
         <v>2897</v>
       </c>
     </row>
-    <row r="706" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="706" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A706" t="s">
         <v>1758</v>
       </c>
@@ -41503,7 +41524,7 @@
         <v>2901</v>
       </c>
     </row>
-    <row r="707" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="707" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A707" t="s">
         <v>1758</v>
       </c>
@@ -41541,7 +41562,7 @@
         <v>2905</v>
       </c>
     </row>
-    <row r="708" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="708" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A708" t="s">
         <v>1758</v>
       </c>
@@ -41573,7 +41594,7 @@
         <v>2910</v>
       </c>
     </row>
-    <row r="709" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="709" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A709" t="s">
         <v>1758</v>
       </c>
@@ -41614,7 +41635,7 @@
         <v>2915</v>
       </c>
     </row>
-    <row r="710" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="710" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A710" t="s">
         <v>1758</v>
       </c>
@@ -41655,7 +41676,7 @@
         <v>2920</v>
       </c>
     </row>
-    <row r="711" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="711" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A711" t="s">
         <v>1758</v>
       </c>
@@ -41696,7 +41717,7 @@
         <v>2924</v>
       </c>
     </row>
-    <row r="712" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="712" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A712" t="s">
         <v>1758</v>
       </c>
@@ -41740,7 +41761,7 @@
         <v>2929</v>
       </c>
     </row>
-    <row r="713" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="713" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A713" t="s">
         <v>1758</v>
       </c>
@@ -41784,7 +41805,7 @@
         <v>2934</v>
       </c>
     </row>
-    <row r="714" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="714" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A714" t="s">
         <v>1758</v>
       </c>
@@ -41825,7 +41846,7 @@
         <v>2939</v>
       </c>
     </row>
-    <row r="715" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="715" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A715" t="s">
         <v>1758</v>
       </c>
@@ -41866,7 +41887,7 @@
         <v>2943</v>
       </c>
     </row>
-    <row r="716" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="716" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A716" t="s">
         <v>1758</v>
       </c>
@@ -41907,7 +41928,7 @@
         <v>2946</v>
       </c>
     </row>
-    <row r="717" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="717" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A717" t="s">
         <v>1758</v>
       </c>
@@ -41992,7 +42013,7 @@
         <v>2955</v>
       </c>
     </row>
-    <row r="719" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="719" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A719" t="s">
         <v>1758</v>
       </c>
@@ -42036,7 +42057,7 @@
         <v>2961</v>
       </c>
     </row>
-    <row r="720" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="720" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A720" t="s">
         <v>1758</v>
       </c>
@@ -42124,7 +42145,7 @@
         <v>2970</v>
       </c>
     </row>
-    <row r="722" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="722" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A722" t="s">
         <v>1758</v>
       </c>
@@ -42165,7 +42186,7 @@
         <v>2974</v>
       </c>
     </row>
-    <row r="723" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="723" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A723" t="s">
         <v>1758</v>
       </c>
@@ -42247,7 +42268,7 @@
         <v>2983</v>
       </c>
     </row>
-    <row r="725" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="725" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A725" t="s">
         <v>1758</v>
       </c>
@@ -42288,7 +42309,7 @@
         <v>2987</v>
       </c>
     </row>
-    <row r="726" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="726" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A726" t="s">
         <v>1758</v>
       </c>
@@ -42367,7 +42388,7 @@
         <v>2999</v>
       </c>
     </row>
-    <row r="728" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="728" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A728" t="s">
         <v>1758</v>
       </c>
@@ -42408,7 +42429,7 @@
         <v>3003</v>
       </c>
     </row>
-    <row r="729" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="729" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A729" t="s">
         <v>1758</v>
       </c>
@@ -42452,7 +42473,7 @@
         <v>3007</v>
       </c>
     </row>
-    <row r="730" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="730" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A730" t="s">
         <v>1758</v>
       </c>
@@ -42496,7 +42517,7 @@
         <v>3011</v>
       </c>
     </row>
-    <row r="731" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="731" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A731" t="s">
         <v>1758</v>
       </c>
@@ -42537,7 +42558,7 @@
         <v>3017</v>
       </c>
     </row>
-    <row r="732" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="732" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A732" t="s">
         <v>1758</v>
       </c>
@@ -42581,7 +42602,7 @@
         <v>3023</v>
       </c>
     </row>
-    <row r="733" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="733" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A733" t="s">
         <v>1758</v>
       </c>
@@ -42625,7 +42646,7 @@
         <v>3029</v>
       </c>
     </row>
-    <row r="734" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="734" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A734" t="s">
         <v>1758</v>
       </c>
@@ -42669,7 +42690,7 @@
         <v>3033</v>
       </c>
     </row>
-    <row r="735" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="735" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A735" t="s">
         <v>1758</v>
       </c>
@@ -42710,7 +42731,7 @@
         <v>3037</v>
       </c>
     </row>
-    <row r="736" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="736" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A736" t="s">
         <v>1758</v>
       </c>
@@ -42751,7 +42772,7 @@
         <v>3041</v>
       </c>
     </row>
-    <row r="737" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="737" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A737" t="s">
         <v>1758</v>
       </c>
@@ -42792,7 +42813,7 @@
         <v>3045</v>
       </c>
     </row>
-    <row r="738" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="738" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A738" t="s">
         <v>1758</v>
       </c>
@@ -42836,7 +42857,7 @@
         <v>3050</v>
       </c>
     </row>
-    <row r="739" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="739" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A739" t="s">
         <v>1758</v>
       </c>
@@ -42880,7 +42901,7 @@
         <v>3054</v>
       </c>
     </row>
-    <row r="740" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="740" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A740" t="s">
         <v>1758</v>
       </c>
@@ -42924,7 +42945,7 @@
         <v>3059</v>
       </c>
     </row>
-    <row r="741" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="741" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A741" t="s">
         <v>1758</v>
       </c>
@@ -42968,7 +42989,7 @@
         <v>3064</v>
       </c>
     </row>
-    <row r="742" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="742" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A742" t="s">
         <v>1758</v>
       </c>
@@ -43012,7 +43033,7 @@
         <v>3068</v>
       </c>
     </row>
-    <row r="743" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="743" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A743" t="s">
         <v>1758</v>
       </c>
@@ -43056,7 +43077,7 @@
         <v>3072</v>
       </c>
     </row>
-    <row r="744" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="744" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A744" t="s">
         <v>1758</v>
       </c>
@@ -43097,7 +43118,7 @@
         <v>3077</v>
       </c>
     </row>
-    <row r="745" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="745" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A745" t="s">
         <v>1758</v>
       </c>
@@ -43135,7 +43156,7 @@
         <v>3082</v>
       </c>
     </row>
-    <row r="746" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="746" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A746" t="s">
         <v>1758</v>
       </c>
@@ -43179,7 +43200,7 @@
         <v>3087</v>
       </c>
     </row>
-    <row r="747" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="747" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A747" t="s">
         <v>1758</v>
       </c>
@@ -43223,7 +43244,7 @@
         <v>3092</v>
       </c>
     </row>
-    <row r="748" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="748" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A748" t="s">
         <v>1758</v>
       </c>
@@ -43267,7 +43288,7 @@
         <v>3097</v>
       </c>
     </row>
-    <row r="749" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="749" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A749" t="s">
         <v>1758</v>
       </c>
@@ -43308,7 +43329,7 @@
         <v>3102</v>
       </c>
     </row>
-    <row r="750" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="750" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A750" t="s">
         <v>1758</v>
       </c>
@@ -43352,7 +43373,7 @@
         <v>3107</v>
       </c>
     </row>
-    <row r="751" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="751" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A751" t="s">
         <v>1758</v>
       </c>
@@ -43396,7 +43417,7 @@
         <v>3112</v>
       </c>
     </row>
-    <row r="752" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="752" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A752" t="s">
         <v>1758</v>
       </c>
@@ -43437,7 +43458,7 @@
         <v>3115</v>
       </c>
     </row>
-    <row r="753" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="753" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A753" t="s">
         <v>1758</v>
       </c>
@@ -43469,7 +43490,7 @@
         <v>3120</v>
       </c>
     </row>
-    <row r="754" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="754" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A754" t="s">
         <v>1758</v>
       </c>
@@ -43513,7 +43534,7 @@
         <v>3126</v>
       </c>
     </row>
-    <row r="755" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="755" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A755" t="s">
         <v>1758</v>
       </c>
@@ -43557,7 +43578,7 @@
         <v>3130</v>
       </c>
     </row>
-    <row r="756" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="756" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A756" t="s">
         <v>1758</v>
       </c>
@@ -43598,7 +43619,7 @@
         <v>3135</v>
       </c>
     </row>
-    <row r="757" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="757" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A757" t="s">
         <v>1758</v>
       </c>
@@ -43636,7 +43657,7 @@
         <v>3140</v>
       </c>
     </row>
-    <row r="758" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="758" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A758" t="s">
         <v>1758</v>
       </c>
@@ -43677,7 +43698,7 @@
         <v>3145</v>
       </c>
     </row>
-    <row r="759" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="759" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A759" t="s">
         <v>1758</v>
       </c>
@@ -43718,7 +43739,7 @@
         <v>3149</v>
       </c>
     </row>
-    <row r="760" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="760" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A760" t="s">
         <v>1758</v>
       </c>
@@ -43762,7 +43783,7 @@
         <v>3153</v>
       </c>
     </row>
-    <row r="761" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="761" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A761" t="s">
         <v>1758</v>
       </c>
@@ -43806,7 +43827,7 @@
         <v>3158</v>
       </c>
     </row>
-    <row r="762" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="762" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A762" t="s">
         <v>1758</v>
       </c>
@@ -43850,7 +43871,7 @@
         <v>3162</v>
       </c>
     </row>
-    <row r="763" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="763" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A763" t="s">
         <v>1758</v>
       </c>
@@ -43894,7 +43915,7 @@
         <v>3166</v>
       </c>
     </row>
-    <row r="764" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="764" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A764" t="s">
         <v>1758</v>
       </c>
@@ -43938,7 +43959,7 @@
         <v>3171</v>
       </c>
     </row>
-    <row r="765" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="765" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A765" t="s">
         <v>1758</v>
       </c>
@@ -43982,7 +44003,7 @@
         <v>3176</v>
       </c>
     </row>
-    <row r="766" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="766" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A766" t="s">
         <v>1758</v>
       </c>
@@ -44026,7 +44047,7 @@
         <v>3181</v>
       </c>
     </row>
-    <row r="767" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="767" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A767" t="s">
         <v>1758</v>
       </c>
@@ -44070,7 +44091,7 @@
         <v>3185</v>
       </c>
     </row>
-    <row r="768" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="768" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A768" t="s">
         <v>1758</v>
       </c>
@@ -44111,7 +44132,7 @@
         <v>3190</v>
       </c>
     </row>
-    <row r="769" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="769" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A769" t="s">
         <v>1758</v>
       </c>
@@ -44155,7 +44176,7 @@
         <v>3195</v>
       </c>
     </row>
-    <row r="770" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="770" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A770" t="s">
         <v>1758</v>
       </c>
@@ -44199,7 +44220,7 @@
         <v>3200</v>
       </c>
     </row>
-    <row r="771" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="771" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A771" t="s">
         <v>1758</v>
       </c>
@@ -44240,7 +44261,7 @@
         <v>3204</v>
       </c>
     </row>
-    <row r="772" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="772" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A772" t="s">
         <v>1758</v>
       </c>
@@ -44275,7 +44296,7 @@
         <v>3208</v>
       </c>
     </row>
-    <row r="773" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="773" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A773" t="s">
         <v>1758</v>
       </c>
@@ -44354,7 +44375,7 @@
         <v>3218</v>
       </c>
     </row>
-    <row r="775" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="775" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A775" t="s">
         <v>1758</v>
       </c>
@@ -44395,7 +44416,7 @@
         <v>3224</v>
       </c>
     </row>
-    <row r="776" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="776" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A776" t="s">
         <v>1758</v>
       </c>
@@ -44439,7 +44460,7 @@
         <v>3229</v>
       </c>
     </row>
-    <row r="777" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="777" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A777" t="s">
         <v>1758</v>
       </c>
@@ -44483,7 +44504,7 @@
         <v>3233</v>
       </c>
     </row>
-    <row r="778" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="778" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A778" t="s">
         <v>1758</v>
       </c>
@@ -44524,7 +44545,7 @@
         <v>3238</v>
       </c>
     </row>
-    <row r="779" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="779" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A779" t="s">
         <v>1758</v>
       </c>
@@ -44565,7 +44586,7 @@
         <v>3242</v>
       </c>
     </row>
-    <row r="780" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="780" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A780" t="s">
         <v>1758</v>
       </c>
@@ -44653,7 +44674,7 @@
         <v>3252</v>
       </c>
     </row>
-    <row r="782" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="782" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A782" t="s">
         <v>1758</v>
       </c>
@@ -44685,7 +44706,7 @@
         <v>3257</v>
       </c>
     </row>
-    <row r="783" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="783" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A783" t="s">
         <v>1758</v>
       </c>
@@ -44723,7 +44744,7 @@
         <v>3262</v>
       </c>
     </row>
-    <row r="784" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="784" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A784" t="s">
         <v>1758</v>
       </c>
@@ -44764,7 +44785,7 @@
         <v>3266</v>
       </c>
     </row>
-    <row r="785" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="785" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A785" t="s">
         <v>1758</v>
       </c>
@@ -44808,7 +44829,7 @@
         <v>3270</v>
       </c>
     </row>
-    <row r="786" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="786" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A786" t="s">
         <v>1758</v>
       </c>
@@ -44849,7 +44870,7 @@
         <v>3275</v>
       </c>
     </row>
-    <row r="787" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="787" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A787" t="s">
         <v>1758</v>
       </c>
@@ -44893,7 +44914,7 @@
         <v>3280</v>
       </c>
     </row>
-    <row r="788" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="788" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A788" t="s">
         <v>1758</v>
       </c>
@@ -44981,7 +45002,7 @@
         <v>3290</v>
       </c>
     </row>
-    <row r="790" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="790" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A790" t="s">
         <v>1758</v>
       </c>
@@ -45022,7 +45043,7 @@
         <v>3294</v>
       </c>
     </row>
-    <row r="791" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="791" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A791" t="s">
         <v>1758</v>
       </c>
@@ -45104,7 +45125,7 @@
         <v>3303</v>
       </c>
     </row>
-    <row r="793" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="793" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A793" t="s">
         <v>1758</v>
       </c>
@@ -45145,7 +45166,7 @@
         <v>3307</v>
       </c>
     </row>
-    <row r="794" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="794" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A794" t="s">
         <v>1758</v>
       </c>
@@ -45189,7 +45210,7 @@
         <v>3311</v>
       </c>
     </row>
-    <row r="795" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="795" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A795" t="s">
         <v>1758</v>
       </c>
@@ -45230,7 +45251,7 @@
         <v>3315</v>
       </c>
     </row>
-    <row r="796" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="796" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A796" t="s">
         <v>1758</v>
       </c>
@@ -45271,7 +45292,7 @@
         <v>3319</v>
       </c>
     </row>
-    <row r="797" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="797" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A797" t="s">
         <v>1758</v>
       </c>
@@ -45312,7 +45333,7 @@
         <v>3325</v>
       </c>
     </row>
-    <row r="798" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="798" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A798" t="s">
         <v>1758</v>
       </c>
@@ -45353,7 +45374,7 @@
         <v>3331</v>
       </c>
     </row>
-    <row r="799" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="799" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A799" t="s">
         <v>1758</v>
       </c>
@@ -45385,7 +45406,7 @@
         <v>3336</v>
       </c>
     </row>
-    <row r="800" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="800" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A800" t="s">
         <v>1758</v>
       </c>
@@ -45426,7 +45447,7 @@
         <v>3340</v>
       </c>
     </row>
-    <row r="801" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="801" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A801" t="s">
         <v>1758</v>
       </c>
@@ -45458,7 +45479,7 @@
         <v>3344</v>
       </c>
     </row>
-    <row r="802" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="802" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A802" t="s">
         <v>1758</v>
       </c>
@@ -45493,7 +45514,7 @@
         <v>3348</v>
       </c>
     </row>
-    <row r="803" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="803" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A803" t="s">
         <v>1758</v>
       </c>
@@ -45528,7 +45549,7 @@
         <v>3353</v>
       </c>
     </row>
-    <row r="804" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="804" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A804" t="s">
         <v>1758</v>
       </c>
@@ -45569,7 +45590,7 @@
         <v>3358</v>
       </c>
     </row>
-    <row r="805" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="805" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A805" t="s">
         <v>1758</v>
       </c>
@@ -45654,7 +45675,7 @@
         <v>3367</v>
       </c>
     </row>
-    <row r="807" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="807" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A807" t="s">
         <v>1758</v>
       </c>
@@ -45733,7 +45754,7 @@
         <v>3374</v>
       </c>
     </row>
-    <row r="809" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="809" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A809" t="s">
         <v>1758</v>
       </c>
@@ -45768,7 +45789,7 @@
         <v>3378</v>
       </c>
     </row>
-    <row r="810" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="810" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A810" t="s">
         <v>1758</v>
       </c>
@@ -45812,7 +45833,7 @@
         <v>3383</v>
       </c>
     </row>
-    <row r="811" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="811" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A811" t="s">
         <v>1758</v>
       </c>
@@ -45856,7 +45877,7 @@
         <v>3389</v>
       </c>
     </row>
-    <row r="812" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="812" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A812" t="s">
         <v>1758</v>
       </c>
@@ -45900,7 +45921,7 @@
         <v>3394</v>
       </c>
     </row>
-    <row r="813" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="813" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A813" t="s">
         <v>1758</v>
       </c>
@@ -45982,7 +46003,7 @@
         <v>3403</v>
       </c>
     </row>
-    <row r="815" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="815" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A815" t="s">
         <v>1758</v>
       </c>
@@ -46064,7 +46085,7 @@
         <v>3415</v>
       </c>
     </row>
-    <row r="817" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="817" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A817" t="s">
         <v>1758</v>
       </c>
@@ -46146,7 +46167,7 @@
         <v>3424</v>
       </c>
     </row>
-    <row r="819" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="819" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A819" t="s">
         <v>1758</v>
       </c>
@@ -46187,7 +46208,7 @@
         <v>3429</v>
       </c>
     </row>
-    <row r="820" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="820" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A820" t="s">
         <v>1758</v>
       </c>
@@ -46228,7 +46249,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="821" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="821" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A821" t="s">
         <v>1758</v>
       </c>
@@ -46272,7 +46293,7 @@
         <v>3435</v>
       </c>
     </row>
-    <row r="822" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="822" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A822" t="s">
         <v>1758</v>
       </c>
@@ -46307,7 +46328,7 @@
         <v>3440</v>
       </c>
     </row>
-    <row r="823" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="823" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A823" t="s">
         <v>1758</v>
       </c>
@@ -46395,7 +46416,7 @@
         <v>3449</v>
       </c>
     </row>
-    <row r="825" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="825" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A825" t="s">
         <v>1758</v>
       </c>
@@ -46436,7 +46457,7 @@
         <v>3454</v>
       </c>
     </row>
-    <row r="826" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="826" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A826" t="s">
         <v>1758</v>
       </c>
@@ -46471,7 +46492,7 @@
         <v>3459</v>
       </c>
     </row>
-    <row r="827" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="827" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A827" t="s">
         <v>1758</v>
       </c>
@@ -46503,7 +46524,7 @@
         <v>3464</v>
       </c>
     </row>
-    <row r="828" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="828" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A828" t="s">
         <v>1758</v>
       </c>
@@ -46541,7 +46562,7 @@
         <v>3470</v>
       </c>
     </row>
-    <row r="829" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="829" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A829" t="s">
         <v>1758</v>
       </c>
@@ -46585,7 +46606,7 @@
         <v>3475</v>
       </c>
     </row>
-    <row r="830" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="830" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A830" t="s">
         <v>1758</v>
       </c>
@@ -46629,7 +46650,7 @@
         <v>3479</v>
       </c>
     </row>
-    <row r="831" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="831" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A831" t="s">
         <v>1758</v>
       </c>
@@ -46673,7 +46694,7 @@
         <v>3483</v>
       </c>
     </row>
-    <row r="832" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="832" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A832" t="s">
         <v>1758</v>
       </c>
@@ -46717,7 +46738,7 @@
         <v>3488</v>
       </c>
     </row>
-    <row r="833" spans="1:18" x14ac:dyDescent="0.3">
+    <row r="833" spans="1:18" hidden="1" x14ac:dyDescent="0.3">
       <c r="A833" t="s">
         <v>1758</v>
       </c>
@@ -46762,6 +46783,16 @@
       </c>
     </row>
   </sheetData>
+  <autoFilter ref="A1:R833" xr:uid="{32D9BDB5-49E3-4F0A-992F-D41F604492EC}">
+    <filterColumn colId="1">
+      <filters>
+        <filter val="Shah Alam"/>
+      </filters>
+    </filterColumn>
+  </autoFilter>
+  <hyperlinks>
+    <hyperlink ref="R15" r:id="rId1" xr:uid="{B4A0B7D9-ABB9-4493-9156-5E19AD0BC89D}"/>
+  </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
 </file>
--- a/listings.tsv.xlsx
+++ b/listings.tsv.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://d.docs.live.net/831e68cdec78212b/Documents/GitHub/haniproperties/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="6" documentId="8_{C8439A61-B804-44A5-B5F8-615007BB98B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{064FCB6B-C229-49C8-92D4-85E0AFAC8D3A}"/>
+  <xr:revisionPtr revIDLastSave="7" documentId="8_{C8439A61-B804-44A5-B5F8-615007BB98B1}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{372BF166-0A64-4D51-9187-8E9659B28056}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{65CABF58-D2E8-4A2E-8EC9-ED571570DEC3}"/>
   </bookViews>
@@ -10504,7 +10504,7 @@
     <t>https://t.me/extremeproperty_listing/19071</t>
   </si>
   <si>
-    <t>image/Vista Alam|Vista Alam1|Vista Alam2</t>
+    <t>image/Vista Alam.jpg|Vista Alam1.jpg|Vista Alam2.jpg</t>
   </si>
 </sst>
 </file>
@@ -11067,6 +11067,10 @@
 </styleSheet>
 </file>
 
+<file path=xl/persons/person.xml><?xml version="1.0" encoding="utf-8"?>
+<personList xmlns="http://schemas.microsoft.com/office/spreadsheetml/2018/threadedcomments" xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main"/>
+</file>
+
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
 <a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
   <a:themeElements>
